--- a/data/monthly_place/【2025年9月】月次配置.xlsx
+++ b/data/monthly_place/【2025年9月】月次配置.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="612" yWindow="600" windowWidth="21792" windowHeight="10812"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="85">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -146,30 +145,155 @@
   <si>
     <t>Instagramストーリーズ</t>
   </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>広告セット予算を使用</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>むぎ歯科</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>はま歯科医院</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>inactive</t>
+  </si>
+  <si>
+    <t>錦糸町矯正歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>整体処 たくみ堂</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>千歳烏山ケンズ歯科</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>GAJUM photo studio</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>モバイルウェブ</t>
+  </si>
+  <si>
+    <t>オステオパシー治療院 field</t>
+  </si>
+  <si>
+    <t>うな蔵 神龍 馬車道店</t>
+  </si>
+  <si>
+    <t>Ramen Room TENROU</t>
+  </si>
+  <si>
+    <t>2025-10-31</t>
+  </si>
+  <si>
+    <t>金町駅前ジャスミン歯科</t>
+  </si>
+  <si>
+    <t>Plaisir</t>
+  </si>
+  <si>
+    <t>ストレッチ&amp;ボディケア m.o.v.e巣鴨店</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>堀田歯科（リンク先変更前）</t>
+  </si>
+  <si>
+    <t>きしかわデンタルオフィス</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>COCORO エステサロン</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>なかはら歯科クリニック</t>
+  </si>
+  <si>
+    <t>割田歯科医院</t>
+  </si>
+  <si>
+    <t>住友歯科医院</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>はんだ歯科医院</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美歯科）</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（マウスピース矯正）</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>銀座トレーニングラボ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -177,36 +301,36 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -495,14 +619,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:AB6"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AB130"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -588,7 +709,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -626,7 +747,7 @@
         <v>1.094787</v>
       </c>
       <c r="M2">
-        <v>79.33333333</v>
+        <v>79.333333330000002</v>
       </c>
       <c r="N2">
         <v>149</v>
@@ -650,22 +771,22 @@
         <v>3</v>
       </c>
       <c r="V2">
-        <v>79.333333</v>
+        <v>79.333332999999996</v>
       </c>
       <c r="W2">
-        <v>1.298701</v>
+        <v>1.2987010000000001</v>
       </c>
       <c r="X2">
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>1.298701</v>
+        <v>1.2987010000000001</v>
       </c>
       <c r="Z2">
-        <v>79.333333</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28">
+        <v>79.333332999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -724,7 +845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -783,7 +904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -812,7 +933,7 @@
         <v>159</v>
       </c>
       <c r="L5">
-        <v>1.069182</v>
+        <v>1.0691820000000001</v>
       </c>
       <c r="N5">
         <v>149</v>
@@ -830,7 +951,7 @@
         <v>170</v>
       </c>
       <c r="S5">
-        <v>570.588235</v>
+        <v>570.58823500000005</v>
       </c>
       <c r="X5">
         <v>0</v>
@@ -842,7 +963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -907,30 +1028,9233 @@
         <v>86.375</v>
       </c>
       <c r="W6">
-        <v>1.381693</v>
+        <v>1.3816930000000001</v>
       </c>
       <c r="X6">
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>1.381693</v>
+        <v>1.3816930000000001</v>
       </c>
       <c r="Z6">
         <v>86.375</v>
       </c>
     </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7">
+        <v>16</v>
+      </c>
+      <c r="L7">
+        <v>1.375</v>
+      </c>
+      <c r="N7" t="s">
+        <v>44</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>12</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>83</v>
+      </c>
+      <c r="R7">
+        <v>22</v>
+      </c>
+      <c r="S7">
+        <v>545.45454500000005</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>83</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>10000</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9">
+        <v>73</v>
+      </c>
+      <c r="L9">
+        <v>1.616438</v>
+      </c>
+      <c r="M9">
+        <v>38.5</v>
+      </c>
+      <c r="N9" t="s">
+        <v>44</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>77</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>83</v>
+      </c>
+      <c r="R9">
+        <v>118</v>
+      </c>
+      <c r="S9">
+        <v>652.542373</v>
+      </c>
+      <c r="T9">
+        <v>2</v>
+      </c>
+      <c r="V9">
+        <v>38.5</v>
+      </c>
+      <c r="W9">
+        <v>1.6949149999999999</v>
+      </c>
+      <c r="X9">
+        <v>2</v>
+      </c>
+      <c r="Y9">
+        <v>1.6949149999999999</v>
+      </c>
+      <c r="Z9">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10">
+        <v>53</v>
+      </c>
+      <c r="J10" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10">
+        <v>2060</v>
+      </c>
+      <c r="L10">
+        <v>3.354854</v>
+      </c>
+      <c r="M10">
+        <v>103.37735849000001</v>
+      </c>
+      <c r="N10" t="s">
+        <v>44</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>5479</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>83</v>
+      </c>
+      <c r="R10">
+        <v>6911</v>
+      </c>
+      <c r="S10">
+        <v>792.79409599999997</v>
+      </c>
+      <c r="T10">
+        <v>53</v>
+      </c>
+      <c r="V10">
+        <v>103.377358</v>
+      </c>
+      <c r="W10">
+        <v>0.76689300000000005</v>
+      </c>
+      <c r="X10">
+        <v>56</v>
+      </c>
+      <c r="Y10">
+        <v>0.81030199999999997</v>
+      </c>
+      <c r="Z10">
+        <v>97.839286000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="N11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>83</v>
+      </c>
+      <c r="R11">
+        <v>2</v>
+      </c>
+      <c r="S11">
+        <v>1000</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12" t="s">
+        <v>36</v>
+      </c>
+      <c r="K12">
+        <v>105</v>
+      </c>
+      <c r="L12">
+        <v>1.209524</v>
+      </c>
+      <c r="M12">
+        <v>91</v>
+      </c>
+      <c r="N12" t="s">
+        <v>44</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>182</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>81</v>
+      </c>
+      <c r="R12">
+        <v>127</v>
+      </c>
+      <c r="S12">
+        <v>1433.070866</v>
+      </c>
+      <c r="T12">
+        <v>2</v>
+      </c>
+      <c r="V12">
+        <v>91</v>
+      </c>
+      <c r="W12">
+        <v>1.574803</v>
+      </c>
+      <c r="X12">
+        <v>2</v>
+      </c>
+      <c r="Y12">
+        <v>1.574803</v>
+      </c>
+      <c r="Z12">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13">
+        <v>39</v>
+      </c>
+      <c r="L13">
+        <v>1.0769230000000001</v>
+      </c>
+      <c r="N13" t="s">
+        <v>44</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>26</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>81</v>
+      </c>
+      <c r="R13">
+        <v>42</v>
+      </c>
+      <c r="S13">
+        <v>619.04761900000005</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="N14" t="s">
+        <v>44</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>81</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15">
+        <v>87</v>
+      </c>
+      <c r="L15">
+        <v>1.1724140000000001</v>
+      </c>
+      <c r="N15" t="s">
+        <v>44</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>50</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>81</v>
+      </c>
+      <c r="R15">
+        <v>102</v>
+      </c>
+      <c r="S15">
+        <v>490.196078</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16">
+        <v>107</v>
+      </c>
+      <c r="J16" t="s">
+        <v>36</v>
+      </c>
+      <c r="K16">
+        <v>5321</v>
+      </c>
+      <c r="L16">
+        <v>1.3035140000000001</v>
+      </c>
+      <c r="M16">
+        <v>53.598130840000003</v>
+      </c>
+      <c r="N16" t="s">
+        <v>44</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>5735</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>81</v>
+      </c>
+      <c r="R16">
+        <v>6936</v>
+      </c>
+      <c r="S16">
+        <v>826.84544400000004</v>
+      </c>
+      <c r="T16">
+        <v>107</v>
+      </c>
+      <c r="V16">
+        <v>53.598131000000002</v>
+      </c>
+      <c r="W16">
+        <v>1.5426759999999999</v>
+      </c>
+      <c r="X16">
+        <v>108</v>
+      </c>
+      <c r="Y16">
+        <v>1.5570930000000001</v>
+      </c>
+      <c r="Z16">
+        <v>53.101852000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17">
+        <v>26</v>
+      </c>
+      <c r="J17" t="s">
+        <v>36</v>
+      </c>
+      <c r="K17">
+        <v>1312</v>
+      </c>
+      <c r="L17">
+        <v>1.2210369999999999</v>
+      </c>
+      <c r="M17">
+        <v>60.07692308</v>
+      </c>
+      <c r="N17" t="s">
+        <v>44</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>1562</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>78</v>
+      </c>
+      <c r="R17">
+        <v>1602</v>
+      </c>
+      <c r="S17">
+        <v>975.03121099999998</v>
+      </c>
+      <c r="T17">
+        <v>26</v>
+      </c>
+      <c r="V17">
+        <v>60.076923000000001</v>
+      </c>
+      <c r="W17">
+        <v>1.6229709999999999</v>
+      </c>
+      <c r="X17">
+        <v>31</v>
+      </c>
+      <c r="Y17">
+        <v>1.9350810000000001</v>
+      </c>
+      <c r="Z17">
+        <v>50.387096999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K18">
+        <v>225</v>
+      </c>
+      <c r="L18">
+        <v>1.177778</v>
+      </c>
+      <c r="M18">
+        <v>168</v>
+      </c>
+      <c r="N18" t="s">
+        <v>44</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>168</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>78</v>
+      </c>
+      <c r="R18">
+        <v>265</v>
+      </c>
+      <c r="S18">
+        <v>633.962264</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>168</v>
+      </c>
+      <c r="W18">
+        <v>0.37735800000000003</v>
+      </c>
+      <c r="X18">
+        <v>2</v>
+      </c>
+      <c r="Y18">
+        <v>0.75471699999999997</v>
+      </c>
+      <c r="Z18">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K19">
+        <v>9</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="N19" t="s">
+        <v>44</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>78</v>
+      </c>
+      <c r="R19">
+        <v>9</v>
+      </c>
+      <c r="S19">
+        <v>222.22222199999999</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20">
+        <v>6</v>
+      </c>
+      <c r="J20" t="s">
+        <v>36</v>
+      </c>
+      <c r="K20">
+        <v>322</v>
+      </c>
+      <c r="L20">
+        <v>1.152174</v>
+      </c>
+      <c r="M20">
+        <v>42.5</v>
+      </c>
+      <c r="N20" t="s">
+        <v>44</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>255</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>78</v>
+      </c>
+      <c r="R20">
+        <v>371</v>
+      </c>
+      <c r="S20">
+        <v>687.33153600000003</v>
+      </c>
+      <c r="T20">
+        <v>6</v>
+      </c>
+      <c r="V20">
+        <v>42.5</v>
+      </c>
+      <c r="W20">
+        <v>1.617251</v>
+      </c>
+      <c r="X20">
+        <v>7</v>
+      </c>
+      <c r="Y20">
+        <v>1.886792</v>
+      </c>
+      <c r="Z20">
+        <v>36.428570999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21">
+        <v>61</v>
+      </c>
+      <c r="J21" t="s">
+        <v>36</v>
+      </c>
+      <c r="K21">
+        <v>2963</v>
+      </c>
+      <c r="L21">
+        <v>1.2436720000000001</v>
+      </c>
+      <c r="M21">
+        <v>68.098360659999997</v>
+      </c>
+      <c r="N21" t="s">
+        <v>44</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>4154</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>78</v>
+      </c>
+      <c r="R21">
+        <v>3685</v>
+      </c>
+      <c r="S21">
+        <v>1127.272727</v>
+      </c>
+      <c r="T21">
+        <v>61</v>
+      </c>
+      <c r="V21">
+        <v>68.098360999999997</v>
+      </c>
+      <c r="W21">
+        <v>1.6553599999999999</v>
+      </c>
+      <c r="X21">
+        <v>66</v>
+      </c>
+      <c r="Y21">
+        <v>1.791045</v>
+      </c>
+      <c r="Z21">
+        <v>62.939394</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22">
+        <v>12</v>
+      </c>
+      <c r="J22" t="s">
+        <v>36</v>
+      </c>
+      <c r="K22">
+        <v>322</v>
+      </c>
+      <c r="L22">
+        <v>1.2763979999999999</v>
+      </c>
+      <c r="M22">
+        <v>25.416666670000001</v>
+      </c>
+      <c r="N22" t="s">
+        <v>44</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>305</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>78</v>
+      </c>
+      <c r="R22">
+        <v>411</v>
+      </c>
+      <c r="S22">
+        <v>742.09245699999997</v>
+      </c>
+      <c r="T22">
+        <v>12</v>
+      </c>
+      <c r="V22">
+        <v>25.416667</v>
+      </c>
+      <c r="W22">
+        <v>2.919708</v>
+      </c>
+      <c r="X22">
+        <v>15</v>
+      </c>
+      <c r="Y22">
+        <v>3.649635</v>
+      </c>
+      <c r="Z22">
+        <v>20.333333</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="N23" t="s">
+        <v>44</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>78</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
+      <c r="J24" t="s">
+        <v>36</v>
+      </c>
+      <c r="K24">
+        <v>82</v>
+      </c>
+      <c r="L24">
+        <v>1.2804880000000001</v>
+      </c>
+      <c r="M24">
+        <v>19.666666670000001</v>
+      </c>
+      <c r="N24" t="s">
+        <v>44</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>59</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>78</v>
+      </c>
+      <c r="R24">
+        <v>105</v>
+      </c>
+      <c r="S24">
+        <v>561.90476200000001</v>
+      </c>
+      <c r="T24">
+        <v>3</v>
+      </c>
+      <c r="V24">
+        <v>19.666667</v>
+      </c>
+      <c r="W24">
+        <v>2.8571430000000002</v>
+      </c>
+      <c r="X24">
+        <v>3</v>
+      </c>
+      <c r="Y24">
+        <v>2.8571430000000002</v>
+      </c>
+      <c r="Z24">
+        <v>19.666667</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25" t="s">
+        <v>36</v>
+      </c>
+      <c r="K25">
+        <v>41</v>
+      </c>
+      <c r="L25">
+        <v>1.097561</v>
+      </c>
+      <c r="M25">
+        <v>8</v>
+      </c>
+      <c r="N25" t="s">
+        <v>44</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>8</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>78</v>
+      </c>
+      <c r="R25">
+        <v>45</v>
+      </c>
+      <c r="S25">
+        <v>177.77777800000001</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="V25">
+        <v>8</v>
+      </c>
+      <c r="W25">
+        <v>2.2222219999999999</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>2.2222219999999999</v>
+      </c>
+      <c r="Z25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26">
+        <v>9</v>
+      </c>
+      <c r="J26" t="s">
+        <v>36</v>
+      </c>
+      <c r="K26">
+        <v>209</v>
+      </c>
+      <c r="L26">
+        <v>1.215311</v>
+      </c>
+      <c r="M26">
+        <v>19.333333329999999</v>
+      </c>
+      <c r="N26" t="s">
+        <v>44</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>174</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>78</v>
+      </c>
+      <c r="R26">
+        <v>254</v>
+      </c>
+      <c r="S26">
+        <v>685.03936999999996</v>
+      </c>
+      <c r="T26">
+        <v>9</v>
+      </c>
+      <c r="V26">
+        <v>19.333333</v>
+      </c>
+      <c r="W26">
+        <v>3.543307</v>
+      </c>
+      <c r="X26">
+        <v>9</v>
+      </c>
+      <c r="Y26">
+        <v>3.543307</v>
+      </c>
+      <c r="Z26">
+        <v>19.333333</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" t="s">
+        <v>34</v>
+      </c>
+      <c r="H27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27">
+        <v>270</v>
+      </c>
+      <c r="J27" t="s">
+        <v>36</v>
+      </c>
+      <c r="K27">
+        <v>3684</v>
+      </c>
+      <c r="L27">
+        <v>1.273887</v>
+      </c>
+      <c r="M27">
+        <v>20.181481479999999</v>
+      </c>
+      <c r="N27" t="s">
+        <v>44</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>5449</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>78</v>
+      </c>
+      <c r="R27">
+        <v>4693</v>
+      </c>
+      <c r="S27">
+        <v>1161.090987</v>
+      </c>
+      <c r="T27">
+        <v>270</v>
+      </c>
+      <c r="V27">
+        <v>20.181481000000002</v>
+      </c>
+      <c r="W27">
+        <v>5.7532500000000004</v>
+      </c>
+      <c r="X27">
+        <v>277</v>
+      </c>
+      <c r="Y27">
+        <v>5.9024080000000003</v>
+      </c>
+      <c r="Z27">
+        <v>19.671479999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" t="s">
+        <v>50</v>
+      </c>
+      <c r="H28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28">
+        <v>61</v>
+      </c>
+      <c r="J28" t="s">
+        <v>36</v>
+      </c>
+      <c r="K28">
+        <v>1448</v>
+      </c>
+      <c r="L28">
+        <v>1.516575</v>
+      </c>
+      <c r="M28">
+        <v>44.032786889999997</v>
+      </c>
+      <c r="N28" t="s">
+        <v>44</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>2686</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R28">
+        <v>2196</v>
+      </c>
+      <c r="S28">
+        <v>1223.132969</v>
+      </c>
+      <c r="T28">
+        <v>61</v>
+      </c>
+      <c r="V28">
+        <v>44.032786999999999</v>
+      </c>
+      <c r="W28">
+        <v>2.7777780000000001</v>
+      </c>
+      <c r="X28">
+        <v>62</v>
+      </c>
+      <c r="Y28">
+        <v>2.823315</v>
+      </c>
+      <c r="Z28">
+        <v>43.322581</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" t="s">
+        <v>50</v>
+      </c>
+      <c r="H29" t="s">
+        <v>35</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>4</v>
+      </c>
+      <c r="N29" t="s">
+        <v>44</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>76</v>
+      </c>
+      <c r="R29">
+        <v>4</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30" t="s">
+        <v>50</v>
+      </c>
+      <c r="H30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30">
+        <v>13</v>
+      </c>
+      <c r="J30" t="s">
+        <v>36</v>
+      </c>
+      <c r="K30">
+        <v>330</v>
+      </c>
+      <c r="L30">
+        <v>1.3696969999999999</v>
+      </c>
+      <c r="M30">
+        <v>27.76923077</v>
+      </c>
+      <c r="N30" t="s">
+        <v>44</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>361</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>76</v>
+      </c>
+      <c r="R30">
+        <v>452</v>
+      </c>
+      <c r="S30">
+        <v>798.67256599999996</v>
+      </c>
+      <c r="T30">
+        <v>13</v>
+      </c>
+      <c r="V30">
+        <v>27.769231000000001</v>
+      </c>
+      <c r="W30">
+        <v>2.8761060000000001</v>
+      </c>
+      <c r="X30">
+        <v>13</v>
+      </c>
+      <c r="Y30">
+        <v>2.8761060000000001</v>
+      </c>
+      <c r="Z30">
+        <v>27.769231000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G31" t="s">
+        <v>50</v>
+      </c>
+      <c r="H31" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31">
+        <v>4</v>
+      </c>
+      <c r="J31" t="s">
+        <v>36</v>
+      </c>
+      <c r="K31">
+        <v>178</v>
+      </c>
+      <c r="L31">
+        <v>1.5168539999999999</v>
+      </c>
+      <c r="M31">
+        <v>29.25</v>
+      </c>
+      <c r="N31" t="s">
+        <v>44</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>117</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>76</v>
+      </c>
+      <c r="R31">
+        <v>270</v>
+      </c>
+      <c r="S31">
+        <v>433.33333299999998</v>
+      </c>
+      <c r="T31">
+        <v>4</v>
+      </c>
+      <c r="V31">
+        <v>29.25</v>
+      </c>
+      <c r="W31">
+        <v>1.481481</v>
+      </c>
+      <c r="X31">
+        <v>4</v>
+      </c>
+      <c r="Y31">
+        <v>1.481481</v>
+      </c>
+      <c r="Z31">
+        <v>29.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" t="s">
+        <v>41</v>
+      </c>
+      <c r="F32" t="s">
+        <v>33</v>
+      </c>
+      <c r="G32" t="s">
+        <v>50</v>
+      </c>
+      <c r="H32" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s">
+        <v>36</v>
+      </c>
+      <c r="K32">
+        <v>693</v>
+      </c>
+      <c r="L32">
+        <v>1.285714</v>
+      </c>
+      <c r="M32">
+        <v>40.047619050000002</v>
+      </c>
+      <c r="N32" t="s">
+        <v>44</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>841</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>76</v>
+      </c>
+      <c r="R32">
+        <v>891</v>
+      </c>
+      <c r="S32">
+        <v>943.88327700000002</v>
+      </c>
+      <c r="T32">
+        <v>21</v>
+      </c>
+      <c r="V32">
+        <v>40.047618999999997</v>
+      </c>
+      <c r="W32">
+        <v>2.3569019999999998</v>
+      </c>
+      <c r="X32">
+        <v>21</v>
+      </c>
+      <c r="Y32">
+        <v>2.3569019999999998</v>
+      </c>
+      <c r="Z32">
+        <v>40.047618999999997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" t="s">
+        <v>50</v>
+      </c>
+      <c r="H33" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33">
+        <v>55</v>
+      </c>
+      <c r="J33" t="s">
+        <v>36</v>
+      </c>
+      <c r="K33">
+        <v>1639</v>
+      </c>
+      <c r="L33">
+        <v>1.257474</v>
+      </c>
+      <c r="M33">
+        <v>43.76363636</v>
+      </c>
+      <c r="N33" t="s">
+        <v>44</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>2407</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>76</v>
+      </c>
+      <c r="R33">
+        <v>2061</v>
+      </c>
+      <c r="S33">
+        <v>1167.87967</v>
+      </c>
+      <c r="T33">
+        <v>55</v>
+      </c>
+      <c r="V33">
+        <v>43.763635999999998</v>
+      </c>
+      <c r="W33">
+        <v>2.6686070000000002</v>
+      </c>
+      <c r="X33">
+        <v>55</v>
+      </c>
+      <c r="Y33">
+        <v>2.6686070000000002</v>
+      </c>
+      <c r="Z33">
+        <v>43.763635999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" t="s">
+        <v>34</v>
+      </c>
+      <c r="H34" t="s">
+        <v>35</v>
+      </c>
+      <c r="I34">
+        <v>29</v>
+      </c>
+      <c r="J34" t="s">
+        <v>36</v>
+      </c>
+      <c r="K34">
+        <v>1718</v>
+      </c>
+      <c r="L34">
+        <v>1.3416760000000001</v>
+      </c>
+      <c r="M34">
+        <v>51.517241380000002</v>
+      </c>
+      <c r="N34" t="s">
+        <v>44</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>1494</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>72</v>
+      </c>
+      <c r="R34">
+        <v>2305</v>
+      </c>
+      <c r="S34">
+        <v>648.15618199999994</v>
+      </c>
+      <c r="T34">
+        <v>29</v>
+      </c>
+      <c r="V34">
+        <v>51.517240999999999</v>
+      </c>
+      <c r="W34">
+        <v>1.2581340000000001</v>
+      </c>
+      <c r="X34">
+        <v>38</v>
+      </c>
+      <c r="Y34">
+        <v>1.64859</v>
+      </c>
+      <c r="Z34">
+        <v>39.315789000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" t="s">
+        <v>39</v>
+      </c>
+      <c r="F35" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" t="s">
+        <v>34</v>
+      </c>
+      <c r="H35" t="s">
+        <v>35</v>
+      </c>
+      <c r="I35">
+        <v>7</v>
+      </c>
+      <c r="J35" t="s">
+        <v>36</v>
+      </c>
+      <c r="K35">
+        <v>430</v>
+      </c>
+      <c r="L35">
+        <v>1.3581399999999999</v>
+      </c>
+      <c r="M35">
+        <v>37</v>
+      </c>
+      <c r="N35" t="s">
+        <v>44</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>259</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>72</v>
+      </c>
+      <c r="R35">
+        <v>584</v>
+      </c>
+      <c r="S35">
+        <v>443.49315100000001</v>
+      </c>
+      <c r="T35">
+        <v>7</v>
+      </c>
+      <c r="V35">
+        <v>37</v>
+      </c>
+      <c r="W35">
+        <v>1.1986300000000001</v>
+      </c>
+      <c r="X35">
+        <v>7</v>
+      </c>
+      <c r="Y35">
+        <v>1.1986300000000001</v>
+      </c>
+      <c r="Z35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" t="s">
+        <v>40</v>
+      </c>
+      <c r="F36" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H36" t="s">
+        <v>35</v>
+      </c>
+      <c r="K36">
+        <v>39</v>
+      </c>
+      <c r="L36">
+        <v>1.3333330000000001</v>
+      </c>
+      <c r="N36" t="s">
+        <v>44</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>9</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>72</v>
+      </c>
+      <c r="R36">
+        <v>52</v>
+      </c>
+      <c r="S36">
+        <v>173.07692299999999</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" t="s">
+        <v>41</v>
+      </c>
+      <c r="F37" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37" t="s">
+        <v>35</v>
+      </c>
+      <c r="I37">
+        <v>11</v>
+      </c>
+      <c r="J37" t="s">
+        <v>36</v>
+      </c>
+      <c r="K37">
+        <v>634</v>
+      </c>
+      <c r="L37">
+        <v>1.3012619999999999</v>
+      </c>
+      <c r="M37">
+        <v>56.090909089999997</v>
+      </c>
+      <c r="N37" t="s">
+        <v>44</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>617</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>72</v>
+      </c>
+      <c r="R37">
+        <v>825</v>
+      </c>
+      <c r="S37">
+        <v>747.87878799999999</v>
+      </c>
+      <c r="T37">
+        <v>11</v>
+      </c>
+      <c r="V37">
+        <v>56.090909000000003</v>
+      </c>
+      <c r="W37">
+        <v>1.3333330000000001</v>
+      </c>
+      <c r="X37">
+        <v>11</v>
+      </c>
+      <c r="Y37">
+        <v>1.3333330000000001</v>
+      </c>
+      <c r="Z37">
+        <v>56.090909000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" t="s">
+        <v>34</v>
+      </c>
+      <c r="H38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38">
+        <v>82</v>
+      </c>
+      <c r="J38" t="s">
+        <v>36</v>
+      </c>
+      <c r="K38">
+        <v>2347</v>
+      </c>
+      <c r="L38">
+        <v>1.443119</v>
+      </c>
+      <c r="M38">
+        <v>44.231707319999998</v>
+      </c>
+      <c r="N38" t="s">
+        <v>44</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>3627</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>72</v>
+      </c>
+      <c r="R38">
+        <v>3387</v>
+      </c>
+      <c r="S38">
+        <v>1070.8591670000001</v>
+      </c>
+      <c r="T38">
+        <v>82</v>
+      </c>
+      <c r="V38">
+        <v>44.231707</v>
+      </c>
+      <c r="W38">
+        <v>2.4210219999999998</v>
+      </c>
+      <c r="X38">
+        <v>88</v>
+      </c>
+      <c r="Y38">
+        <v>2.598169</v>
+      </c>
+      <c r="Z38">
+        <v>41.215909000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" t="s">
+        <v>74</v>
+      </c>
+      <c r="D39" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" t="s">
+        <v>34</v>
+      </c>
+      <c r="H39" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39">
+        <v>49</v>
+      </c>
+      <c r="J39" t="s">
+        <v>36</v>
+      </c>
+      <c r="K39">
+        <v>1639</v>
+      </c>
+      <c r="L39">
+        <v>1.487492</v>
+      </c>
+      <c r="M39">
+        <v>36.408163270000003</v>
+      </c>
+      <c r="N39" t="s">
+        <v>44</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>1784</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>72</v>
+      </c>
+      <c r="R39">
+        <v>2438</v>
+      </c>
+      <c r="S39">
+        <v>731.74733400000002</v>
+      </c>
+      <c r="T39">
+        <v>49</v>
+      </c>
+      <c r="V39">
+        <v>36.408163000000002</v>
+      </c>
+      <c r="W39">
+        <v>2.0098440000000002</v>
+      </c>
+      <c r="X39">
+        <v>62</v>
+      </c>
+      <c r="Y39">
+        <v>2.5430679999999999</v>
+      </c>
+      <c r="Z39">
+        <v>28.774194000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" t="s">
+        <v>59</v>
+      </c>
+      <c r="G40" t="s">
+        <v>34</v>
+      </c>
+      <c r="H40" t="s">
+        <v>35</v>
+      </c>
+      <c r="K40">
+        <v>3</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="N40" t="s">
+        <v>44</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>5</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>72</v>
+      </c>
+      <c r="R40">
+        <v>3</v>
+      </c>
+      <c r="S40">
+        <v>1666.666667</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" t="s">
+        <v>39</v>
+      </c>
+      <c r="F41" t="s">
+        <v>33</v>
+      </c>
+      <c r="G41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H41" t="s">
+        <v>35</v>
+      </c>
+      <c r="I41">
+        <v>7</v>
+      </c>
+      <c r="J41" t="s">
+        <v>36</v>
+      </c>
+      <c r="K41">
+        <v>363</v>
+      </c>
+      <c r="L41">
+        <v>1.3884300000000001</v>
+      </c>
+      <c r="M41">
+        <v>36.285714290000001</v>
+      </c>
+      <c r="N41" t="s">
+        <v>44</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>254</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>72</v>
+      </c>
+      <c r="R41">
+        <v>504</v>
+      </c>
+      <c r="S41">
+        <v>503.968254</v>
+      </c>
+      <c r="T41">
+        <v>7</v>
+      </c>
+      <c r="V41">
+        <v>36.285713999999999</v>
+      </c>
+      <c r="W41">
+        <v>1.388889</v>
+      </c>
+      <c r="X41">
+        <v>7</v>
+      </c>
+      <c r="Y41">
+        <v>1.388889</v>
+      </c>
+      <c r="Z41">
+        <v>36.285713999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" t="s">
+        <v>74</v>
+      </c>
+      <c r="D42" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" t="s">
+        <v>34</v>
+      </c>
+      <c r="H42" t="s">
+        <v>35</v>
+      </c>
+      <c r="K42">
+        <v>63</v>
+      </c>
+      <c r="L42">
+        <v>1.2380949999999999</v>
+      </c>
+      <c r="N42" t="s">
+        <v>44</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>13</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>72</v>
+      </c>
+      <c r="R42">
+        <v>78</v>
+      </c>
+      <c r="S42">
+        <v>166.66666699999999</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" t="s">
+        <v>41</v>
+      </c>
+      <c r="F43" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" t="s">
+        <v>34</v>
+      </c>
+      <c r="H43" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43">
+        <v>20</v>
+      </c>
+      <c r="J43" t="s">
+        <v>36</v>
+      </c>
+      <c r="K43">
+        <v>503</v>
+      </c>
+      <c r="L43">
+        <v>1.3101389999999999</v>
+      </c>
+      <c r="M43">
+        <v>27.3</v>
+      </c>
+      <c r="N43" t="s">
+        <v>44</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>546</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>72</v>
+      </c>
+      <c r="R43">
+        <v>659</v>
+      </c>
+      <c r="S43">
+        <v>828.52807299999995</v>
+      </c>
+      <c r="T43">
+        <v>20</v>
+      </c>
+      <c r="V43">
+        <v>27.3</v>
+      </c>
+      <c r="W43">
+        <v>3.0349010000000001</v>
+      </c>
+      <c r="X43">
+        <v>23</v>
+      </c>
+      <c r="Y43">
+        <v>3.4901369999999998</v>
+      </c>
+      <c r="Z43">
+        <v>23.739129999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" t="s">
+        <v>74</v>
+      </c>
+      <c r="D44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44" t="s">
+        <v>33</v>
+      </c>
+      <c r="G44" t="s">
+        <v>34</v>
+      </c>
+      <c r="H44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I44">
+        <v>101</v>
+      </c>
+      <c r="J44" t="s">
+        <v>36</v>
+      </c>
+      <c r="K44">
+        <v>1787</v>
+      </c>
+      <c r="L44">
+        <v>1.5987690000000001</v>
+      </c>
+      <c r="M44">
+        <v>32.950495050000001</v>
+      </c>
+      <c r="N44" t="s">
+        <v>44</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>3328</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>72</v>
+      </c>
+      <c r="R44">
+        <v>2857</v>
+      </c>
+      <c r="S44">
+        <v>1164.8582429999999</v>
+      </c>
+      <c r="T44">
+        <v>101</v>
+      </c>
+      <c r="V44">
+        <v>32.950494999999997</v>
+      </c>
+      <c r="W44">
+        <v>3.535177</v>
+      </c>
+      <c r="X44">
+        <v>111</v>
+      </c>
+      <c r="Y44">
+        <v>3.8851939999999998</v>
+      </c>
+      <c r="Z44">
+        <v>29.981981999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" t="s">
+        <v>73</v>
+      </c>
+      <c r="D45" t="s">
+        <v>31</v>
+      </c>
+      <c r="E45" t="s">
+        <v>32</v>
+      </c>
+      <c r="F45" t="s">
+        <v>33</v>
+      </c>
+      <c r="G45" t="s">
+        <v>34</v>
+      </c>
+      <c r="H45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45">
+        <v>2</v>
+      </c>
+      <c r="J45" t="s">
+        <v>36</v>
+      </c>
+      <c r="K45">
+        <v>166</v>
+      </c>
+      <c r="L45">
+        <v>1.2228920000000001</v>
+      </c>
+      <c r="M45">
+        <v>73</v>
+      </c>
+      <c r="N45" t="s">
+        <v>44</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>146</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>72</v>
+      </c>
+      <c r="R45">
+        <v>203</v>
+      </c>
+      <c r="S45">
+        <v>719.21182299999998</v>
+      </c>
+      <c r="T45">
+        <v>2</v>
+      </c>
+      <c r="V45">
+        <v>73</v>
+      </c>
+      <c r="W45">
+        <v>0.98522200000000004</v>
+      </c>
+      <c r="X45">
+        <v>2</v>
+      </c>
+      <c r="Y45">
+        <v>0.98522200000000004</v>
+      </c>
+      <c r="Z45">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46" t="s">
+        <v>39</v>
+      </c>
+      <c r="F46" t="s">
+        <v>33</v>
+      </c>
+      <c r="G46" t="s">
+        <v>34</v>
+      </c>
+      <c r="H46" t="s">
+        <v>35</v>
+      </c>
+      <c r="K46">
+        <v>36</v>
+      </c>
+      <c r="L46">
+        <v>1.3333330000000001</v>
+      </c>
+      <c r="N46" t="s">
+        <v>44</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>17</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>72</v>
+      </c>
+      <c r="R46">
+        <v>48</v>
+      </c>
+      <c r="S46">
+        <v>354.16666700000002</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" t="s">
+        <v>73</v>
+      </c>
+      <c r="D47" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47" t="s">
+        <v>40</v>
+      </c>
+      <c r="F47" t="s">
+        <v>33</v>
+      </c>
+      <c r="G47" t="s">
+        <v>34</v>
+      </c>
+      <c r="H47" t="s">
+        <v>35</v>
+      </c>
+      <c r="K47">
+        <v>13</v>
+      </c>
+      <c r="L47">
+        <v>1.3846149999999999</v>
+      </c>
+      <c r="N47" t="s">
+        <v>44</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>3</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>72</v>
+      </c>
+      <c r="R47">
+        <v>18</v>
+      </c>
+      <c r="S47">
+        <v>166.66666699999999</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" t="s">
+        <v>41</v>
+      </c>
+      <c r="F48" t="s">
+        <v>33</v>
+      </c>
+      <c r="G48" t="s">
+        <v>34</v>
+      </c>
+      <c r="H48" t="s">
+        <v>35</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48" t="s">
+        <v>36</v>
+      </c>
+      <c r="K48">
+        <v>63</v>
+      </c>
+      <c r="L48">
+        <v>1.3333330000000001</v>
+      </c>
+      <c r="M48">
+        <v>57</v>
+      </c>
+      <c r="N48" t="s">
+        <v>44</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>57</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>72</v>
+      </c>
+      <c r="R48">
+        <v>84</v>
+      </c>
+      <c r="S48">
+        <v>678.57142899999997</v>
+      </c>
+      <c r="T48">
+        <v>1</v>
+      </c>
+      <c r="V48">
+        <v>57</v>
+      </c>
+      <c r="W48">
+        <v>1.1904760000000001</v>
+      </c>
+      <c r="X48">
+        <v>2</v>
+      </c>
+      <c r="Y48">
+        <v>2.3809520000000002</v>
+      </c>
+      <c r="Z48">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" t="s">
+        <v>29</v>
+      </c>
+      <c r="C49" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" t="s">
+        <v>42</v>
+      </c>
+      <c r="F49" t="s">
+        <v>33</v>
+      </c>
+      <c r="G49" t="s">
+        <v>34</v>
+      </c>
+      <c r="H49" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49">
+        <v>227</v>
+      </c>
+      <c r="J49" t="s">
+        <v>36</v>
+      </c>
+      <c r="K49">
+        <v>4408</v>
+      </c>
+      <c r="L49">
+        <v>1.36774</v>
+      </c>
+      <c r="M49">
+        <v>25.85022026</v>
+      </c>
+      <c r="N49" t="s">
+        <v>44</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>5868</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>72</v>
+      </c>
+      <c r="R49">
+        <v>6029</v>
+      </c>
+      <c r="S49">
+        <v>973.29573700000003</v>
+      </c>
+      <c r="T49">
+        <v>227</v>
+      </c>
+      <c r="V49">
+        <v>25.85022</v>
+      </c>
+      <c r="W49">
+        <v>3.7651349999999999</v>
+      </c>
+      <c r="X49">
+        <v>234</v>
+      </c>
+      <c r="Y49">
+        <v>3.8812410000000002</v>
+      </c>
+      <c r="Z49">
+        <v>25.076923000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>28</v>
+      </c>
+      <c r="B50" t="s">
+        <v>29</v>
+      </c>
+      <c r="C50" t="s">
+        <v>71</v>
+      </c>
+      <c r="D50" t="s">
+        <v>31</v>
+      </c>
+      <c r="E50" t="s">
+        <v>32</v>
+      </c>
+      <c r="F50" t="s">
+        <v>33</v>
+      </c>
+      <c r="G50" t="s">
+        <v>34</v>
+      </c>
+      <c r="H50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I50">
+        <v>99</v>
+      </c>
+      <c r="J50" t="s">
+        <v>36</v>
+      </c>
+      <c r="K50">
+        <v>1811</v>
+      </c>
+      <c r="L50">
+        <v>1.451684</v>
+      </c>
+      <c r="M50">
+        <v>29.848484849999998</v>
+      </c>
+      <c r="N50" t="s">
+        <v>44</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>2955</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>70</v>
+      </c>
+      <c r="R50">
+        <v>2629</v>
+      </c>
+      <c r="S50">
+        <v>1124.0015209999999</v>
+      </c>
+      <c r="T50">
+        <v>99</v>
+      </c>
+      <c r="V50">
+        <v>29.848485</v>
+      </c>
+      <c r="W50">
+        <v>3.7656900000000002</v>
+      </c>
+      <c r="X50">
+        <v>104</v>
+      </c>
+      <c r="Y50">
+        <v>3.9558770000000001</v>
+      </c>
+      <c r="Z50">
+        <v>28.413461999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" t="s">
+        <v>71</v>
+      </c>
+      <c r="D51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51" t="s">
+        <v>59</v>
+      </c>
+      <c r="G51" t="s">
+        <v>34</v>
+      </c>
+      <c r="H51" t="s">
+        <v>35</v>
+      </c>
+      <c r="K51">
+        <v>2</v>
+      </c>
+      <c r="L51">
+        <v>1.5</v>
+      </c>
+      <c r="N51" t="s">
+        <v>44</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>2</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>70</v>
+      </c>
+      <c r="R51">
+        <v>3</v>
+      </c>
+      <c r="S51">
+        <v>666.66666699999996</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>28</v>
+      </c>
+      <c r="B52" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" t="s">
+        <v>71</v>
+      </c>
+      <c r="D52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" t="s">
+        <v>39</v>
+      </c>
+      <c r="F52" t="s">
+        <v>33</v>
+      </c>
+      <c r="G52" t="s">
+        <v>34</v>
+      </c>
+      <c r="H52" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52">
+        <v>5</v>
+      </c>
+      <c r="J52" t="s">
+        <v>36</v>
+      </c>
+      <c r="K52">
+        <v>190</v>
+      </c>
+      <c r="L52">
+        <v>1.294737</v>
+      </c>
+      <c r="M52">
+        <v>33</v>
+      </c>
+      <c r="N52" t="s">
+        <v>44</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>165</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>70</v>
+      </c>
+      <c r="R52">
+        <v>246</v>
+      </c>
+      <c r="S52">
+        <v>670.73170700000003</v>
+      </c>
+      <c r="T52">
+        <v>5</v>
+      </c>
+      <c r="V52">
+        <v>33</v>
+      </c>
+      <c r="W52">
+        <v>2.0325199999999999</v>
+      </c>
+      <c r="X52">
+        <v>5</v>
+      </c>
+      <c r="Y52">
+        <v>2.0325199999999999</v>
+      </c>
+      <c r="Z52">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>28</v>
+      </c>
+      <c r="B53" t="s">
+        <v>29</v>
+      </c>
+      <c r="C53" t="s">
+        <v>71</v>
+      </c>
+      <c r="D53" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" t="s">
+        <v>35</v>
+      </c>
+      <c r="I53">
+        <v>2</v>
+      </c>
+      <c r="J53" t="s">
+        <v>36</v>
+      </c>
+      <c r="K53">
+        <v>105</v>
+      </c>
+      <c r="L53">
+        <v>1.2285710000000001</v>
+      </c>
+      <c r="M53">
+        <v>24.5</v>
+      </c>
+      <c r="N53" t="s">
+        <v>44</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>49</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>70</v>
+      </c>
+      <c r="R53">
+        <v>129</v>
+      </c>
+      <c r="S53">
+        <v>379.84496100000001</v>
+      </c>
+      <c r="T53">
+        <v>2</v>
+      </c>
+      <c r="V53">
+        <v>24.5</v>
+      </c>
+      <c r="W53">
+        <v>1.5503880000000001</v>
+      </c>
+      <c r="X53">
+        <v>3</v>
+      </c>
+      <c r="Y53">
+        <v>2.3255810000000001</v>
+      </c>
+      <c r="Z53">
+        <v>16.333333</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>28</v>
+      </c>
+      <c r="B54" t="s">
+        <v>29</v>
+      </c>
+      <c r="C54" t="s">
+        <v>71</v>
+      </c>
+      <c r="D54" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54" t="s">
+        <v>41</v>
+      </c>
+      <c r="F54" t="s">
+        <v>33</v>
+      </c>
+      <c r="G54" t="s">
+        <v>34</v>
+      </c>
+      <c r="H54" t="s">
+        <v>35</v>
+      </c>
+      <c r="I54">
+        <v>30</v>
+      </c>
+      <c r="J54" t="s">
+        <v>36</v>
+      </c>
+      <c r="K54">
+        <v>613</v>
+      </c>
+      <c r="L54">
+        <v>1.3327899999999999</v>
+      </c>
+      <c r="M54">
+        <v>33.666666669999998</v>
+      </c>
+      <c r="N54" t="s">
+        <v>44</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>1010</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>70</v>
+      </c>
+      <c r="R54">
+        <v>817</v>
+      </c>
+      <c r="S54">
+        <v>1236.23011</v>
+      </c>
+      <c r="T54">
+        <v>30</v>
+      </c>
+      <c r="V54">
+        <v>33.666666999999997</v>
+      </c>
+      <c r="W54">
+        <v>3.6719710000000001</v>
+      </c>
+      <c r="X54">
+        <v>34</v>
+      </c>
+      <c r="Y54">
+        <v>4.1615669999999998</v>
+      </c>
+      <c r="Z54">
+        <v>29.705881999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>28</v>
+      </c>
+      <c r="B55" t="s">
+        <v>29</v>
+      </c>
+      <c r="C55" t="s">
+        <v>71</v>
+      </c>
+      <c r="D55" t="s">
+        <v>31</v>
+      </c>
+      <c r="E55" t="s">
+        <v>42</v>
+      </c>
+      <c r="F55" t="s">
+        <v>33</v>
+      </c>
+      <c r="G55" t="s">
+        <v>34</v>
+      </c>
+      <c r="H55" t="s">
+        <v>35</v>
+      </c>
+      <c r="I55">
+        <v>63</v>
+      </c>
+      <c r="J55" t="s">
+        <v>36</v>
+      </c>
+      <c r="K55">
+        <v>1008</v>
+      </c>
+      <c r="L55">
+        <v>1.285714</v>
+      </c>
+      <c r="M55">
+        <v>33.984126979999999</v>
+      </c>
+      <c r="N55" t="s">
+        <v>44</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>2141</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>70</v>
+      </c>
+      <c r="R55">
+        <v>1296</v>
+      </c>
+      <c r="S55">
+        <v>1652.006173</v>
+      </c>
+      <c r="T55">
+        <v>63</v>
+      </c>
+      <c r="V55">
+        <v>33.984127000000001</v>
+      </c>
+      <c r="W55">
+        <v>4.8611110000000002</v>
+      </c>
+      <c r="X55">
+        <v>71</v>
+      </c>
+      <c r="Y55">
+        <v>5.4783949999999999</v>
+      </c>
+      <c r="Z55">
+        <v>30.15493</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>28</v>
+      </c>
+      <c r="B56" t="s">
+        <v>29</v>
+      </c>
+      <c r="C56" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56" t="s">
+        <v>31</v>
+      </c>
+      <c r="E56" t="s">
+        <v>42</v>
+      </c>
+      <c r="F56" t="s">
+        <v>59</v>
+      </c>
+      <c r="G56" t="s">
+        <v>34</v>
+      </c>
+      <c r="H56" t="s">
+        <v>35</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="N56" t="s">
+        <v>44</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>2</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>70</v>
+      </c>
+      <c r="R56">
+        <v>1</v>
+      </c>
+      <c r="S56">
+        <v>2000</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>28</v>
+      </c>
+      <c r="B57" t="s">
+        <v>29</v>
+      </c>
+      <c r="C57" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" t="s">
+        <v>32</v>
+      </c>
+      <c r="F57" t="s">
+        <v>33</v>
+      </c>
+      <c r="G57" t="s">
+        <v>50</v>
+      </c>
+      <c r="H57" t="s">
+        <v>35</v>
+      </c>
+      <c r="I57">
+        <v>6</v>
+      </c>
+      <c r="J57" t="s">
+        <v>36</v>
+      </c>
+      <c r="K57">
+        <v>218</v>
+      </c>
+      <c r="L57">
+        <v>1.2935779999999999</v>
+      </c>
+      <c r="M57">
+        <v>60.666666669999998</v>
+      </c>
+      <c r="N57" t="s">
+        <v>44</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>364</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>67</v>
+      </c>
+      <c r="R57">
+        <v>282</v>
+      </c>
+      <c r="S57">
+        <v>1290.7801420000001</v>
+      </c>
+      <c r="T57">
+        <v>6</v>
+      </c>
+      <c r="V57">
+        <v>60.666666999999997</v>
+      </c>
+      <c r="W57">
+        <v>2.1276600000000001</v>
+      </c>
+      <c r="X57">
+        <v>6</v>
+      </c>
+      <c r="Y57">
+        <v>2.1276600000000001</v>
+      </c>
+      <c r="Z57">
+        <v>60.666666999999997</v>
+      </c>
+      <c r="AA57">
+        <v>4</v>
+      </c>
+      <c r="AB57">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>28</v>
+      </c>
+      <c r="B58" t="s">
+        <v>29</v>
+      </c>
+      <c r="C58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D58" t="s">
+        <v>31</v>
+      </c>
+      <c r="E58" t="s">
+        <v>39</v>
+      </c>
+      <c r="F58" t="s">
+        <v>33</v>
+      </c>
+      <c r="G58" t="s">
+        <v>50</v>
+      </c>
+      <c r="H58" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58">
+        <v>3</v>
+      </c>
+      <c r="J58" t="s">
+        <v>36</v>
+      </c>
+      <c r="K58">
+        <v>118</v>
+      </c>
+      <c r="L58">
+        <v>1.20339</v>
+      </c>
+      <c r="M58">
+        <v>32.666666669999998</v>
+      </c>
+      <c r="N58" t="s">
+        <v>44</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>98</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>67</v>
+      </c>
+      <c r="R58">
+        <v>142</v>
+      </c>
+      <c r="S58">
+        <v>690.14084500000001</v>
+      </c>
+      <c r="T58">
+        <v>3</v>
+      </c>
+      <c r="V58">
+        <v>32.666666999999997</v>
+      </c>
+      <c r="W58">
+        <v>2.112676</v>
+      </c>
+      <c r="X58">
+        <v>3</v>
+      </c>
+      <c r="Y58">
+        <v>2.112676</v>
+      </c>
+      <c r="Z58">
+        <v>32.666666999999997</v>
+      </c>
+      <c r="AA58">
+        <v>1</v>
+      </c>
+      <c r="AB58">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>28</v>
+      </c>
+      <c r="B59" t="s">
+        <v>29</v>
+      </c>
+      <c r="C59" t="s">
+        <v>69</v>
+      </c>
+      <c r="D59" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59" t="s">
+        <v>40</v>
+      </c>
+      <c r="F59" t="s">
+        <v>33</v>
+      </c>
+      <c r="G59" t="s">
+        <v>50</v>
+      </c>
+      <c r="H59" t="s">
+        <v>35</v>
+      </c>
+      <c r="K59">
+        <v>12</v>
+      </c>
+      <c r="L59">
+        <v>1.25</v>
+      </c>
+      <c r="N59" t="s">
+        <v>44</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>2</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>67</v>
+      </c>
+      <c r="R59">
+        <v>15</v>
+      </c>
+      <c r="S59">
+        <v>133.33333300000001</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>28</v>
+      </c>
+      <c r="B60" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" t="s">
+        <v>69</v>
+      </c>
+      <c r="D60" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" t="s">
+        <v>41</v>
+      </c>
+      <c r="F60" t="s">
+        <v>33</v>
+      </c>
+      <c r="G60" t="s">
+        <v>50</v>
+      </c>
+      <c r="H60" t="s">
+        <v>35</v>
+      </c>
+      <c r="I60">
+        <v>6</v>
+      </c>
+      <c r="J60" t="s">
+        <v>36</v>
+      </c>
+      <c r="K60">
+        <v>196</v>
+      </c>
+      <c r="L60">
+        <v>1.183673</v>
+      </c>
+      <c r="M60">
+        <v>37.833333330000002</v>
+      </c>
+      <c r="N60" t="s">
+        <v>44</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>227</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>67</v>
+      </c>
+      <c r="R60">
+        <v>232</v>
+      </c>
+      <c r="S60">
+        <v>978.44827599999996</v>
+      </c>
+      <c r="T60">
+        <v>6</v>
+      </c>
+      <c r="V60">
+        <v>37.833333000000003</v>
+      </c>
+      <c r="W60">
+        <v>2.5862069999999999</v>
+      </c>
+      <c r="X60">
+        <v>6</v>
+      </c>
+      <c r="Y60">
+        <v>2.5862069999999999</v>
+      </c>
+      <c r="Z60">
+        <v>37.833333000000003</v>
+      </c>
+      <c r="AA60">
+        <v>6</v>
+      </c>
+      <c r="AB60">
+        <v>37.833333000000003</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>28</v>
+      </c>
+      <c r="B61" t="s">
+        <v>29</v>
+      </c>
+      <c r="C61" t="s">
+        <v>69</v>
+      </c>
+      <c r="D61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E61" t="s">
+        <v>42</v>
+      </c>
+      <c r="F61" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61" t="s">
+        <v>50</v>
+      </c>
+      <c r="H61" t="s">
+        <v>35</v>
+      </c>
+      <c r="I61">
+        <v>114</v>
+      </c>
+      <c r="J61" t="s">
+        <v>36</v>
+      </c>
+      <c r="K61">
+        <v>3827</v>
+      </c>
+      <c r="L61">
+        <v>1.283512</v>
+      </c>
+      <c r="M61">
+        <v>53.280701749999999</v>
+      </c>
+      <c r="N61" t="s">
+        <v>44</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>6074</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>67</v>
+      </c>
+      <c r="R61">
+        <v>4912</v>
+      </c>
+      <c r="S61">
+        <v>1236.5635179999999</v>
+      </c>
+      <c r="T61">
+        <v>114</v>
+      </c>
+      <c r="V61">
+        <v>53.280701999999998</v>
+      </c>
+      <c r="W61">
+        <v>2.3208470000000001</v>
+      </c>
+      <c r="X61">
+        <v>119</v>
+      </c>
+      <c r="Y61">
+        <v>2.4226380000000001</v>
+      </c>
+      <c r="Z61">
+        <v>51.042017000000001</v>
+      </c>
+      <c r="AA61">
+        <v>53</v>
+      </c>
+      <c r="AB61">
+        <v>114.603774</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>28</v>
+      </c>
+      <c r="B62" t="s">
+        <v>29</v>
+      </c>
+      <c r="C62" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62" t="s">
+        <v>31</v>
+      </c>
+      <c r="E62" t="s">
+        <v>32</v>
+      </c>
+      <c r="F62" t="s">
+        <v>33</v>
+      </c>
+      <c r="G62" t="s">
+        <v>50</v>
+      </c>
+      <c r="H62" t="s">
+        <v>35</v>
+      </c>
+      <c r="I62">
+        <v>22</v>
+      </c>
+      <c r="J62" t="s">
+        <v>36</v>
+      </c>
+      <c r="K62">
+        <v>785</v>
+      </c>
+      <c r="L62">
+        <v>1.3936310000000001</v>
+      </c>
+      <c r="M62">
+        <v>46.454545449999998</v>
+      </c>
+      <c r="N62" t="s">
+        <v>44</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>1022</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>67</v>
+      </c>
+      <c r="R62">
+        <v>1094</v>
+      </c>
+      <c r="S62">
+        <v>934.18647199999998</v>
+      </c>
+      <c r="T62">
+        <v>22</v>
+      </c>
+      <c r="V62">
+        <v>46.454545000000003</v>
+      </c>
+      <c r="W62">
+        <v>2.0109689999999998</v>
+      </c>
+      <c r="X62">
+        <v>24</v>
+      </c>
+      <c r="Y62">
+        <v>2.193784</v>
+      </c>
+      <c r="Z62">
+        <v>42.583333000000003</v>
+      </c>
+      <c r="AA62">
+        <v>19</v>
+      </c>
+      <c r="AB62">
+        <v>53.789473999999998</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>28</v>
+      </c>
+      <c r="B63" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63" t="s">
+        <v>68</v>
+      </c>
+      <c r="D63" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63" t="s">
+        <v>32</v>
+      </c>
+      <c r="F63" t="s">
+        <v>59</v>
+      </c>
+      <c r="G63" t="s">
+        <v>50</v>
+      </c>
+      <c r="H63" t="s">
+        <v>35</v>
+      </c>
+      <c r="K63">
+        <v>1</v>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+      <c r="N63" t="s">
+        <v>44</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>67</v>
+      </c>
+      <c r="R63">
+        <v>1</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>28</v>
+      </c>
+      <c r="B64" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" t="s">
+        <v>31</v>
+      </c>
+      <c r="E64" t="s">
+        <v>39</v>
+      </c>
+      <c r="F64" t="s">
+        <v>33</v>
+      </c>
+      <c r="G64" t="s">
+        <v>50</v>
+      </c>
+      <c r="H64" t="s">
+        <v>35</v>
+      </c>
+      <c r="I64">
+        <v>2</v>
+      </c>
+      <c r="J64" t="s">
+        <v>36</v>
+      </c>
+      <c r="K64">
+        <v>159</v>
+      </c>
+      <c r="L64">
+        <v>1.2767299999999999</v>
+      </c>
+      <c r="M64">
+        <v>51</v>
+      </c>
+      <c r="N64" t="s">
+        <v>44</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>102</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>67</v>
+      </c>
+      <c r="R64">
+        <v>203</v>
+      </c>
+      <c r="S64">
+        <v>502.463054</v>
+      </c>
+      <c r="T64">
+        <v>2</v>
+      </c>
+      <c r="V64">
+        <v>51</v>
+      </c>
+      <c r="W64">
+        <v>0.98522200000000004</v>
+      </c>
+      <c r="X64">
+        <v>2</v>
+      </c>
+      <c r="Y64">
+        <v>0.98522200000000004</v>
+      </c>
+      <c r="Z64">
+        <v>51</v>
+      </c>
+      <c r="AA64">
+        <v>1</v>
+      </c>
+      <c r="AB64">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>28</v>
+      </c>
+      <c r="B65" t="s">
+        <v>29</v>
+      </c>
+      <c r="C65" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" t="s">
+        <v>31</v>
+      </c>
+      <c r="E65" t="s">
+        <v>40</v>
+      </c>
+      <c r="F65" t="s">
+        <v>33</v>
+      </c>
+      <c r="G65" t="s">
+        <v>50</v>
+      </c>
+      <c r="H65" t="s">
+        <v>35</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+      <c r="J65" t="s">
+        <v>36</v>
+      </c>
+      <c r="K65">
+        <v>69</v>
+      </c>
+      <c r="L65">
+        <v>1.289855</v>
+      </c>
+      <c r="M65">
+        <v>16</v>
+      </c>
+      <c r="N65" t="s">
+        <v>44</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>16</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>67</v>
+      </c>
+      <c r="R65">
+        <v>89</v>
+      </c>
+      <c r="S65">
+        <v>179.77528100000001</v>
+      </c>
+      <c r="T65">
+        <v>1</v>
+      </c>
+      <c r="V65">
+        <v>16</v>
+      </c>
+      <c r="W65">
+        <v>1.123596</v>
+      </c>
+      <c r="X65">
+        <v>1</v>
+      </c>
+      <c r="Y65">
+        <v>1.123596</v>
+      </c>
+      <c r="Z65">
+        <v>16</v>
+      </c>
+      <c r="AA65">
+        <v>1</v>
+      </c>
+      <c r="AB65">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>28</v>
+      </c>
+      <c r="B66" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66" t="s">
+        <v>31</v>
+      </c>
+      <c r="E66" t="s">
+        <v>41</v>
+      </c>
+      <c r="F66" t="s">
+        <v>33</v>
+      </c>
+      <c r="G66" t="s">
+        <v>50</v>
+      </c>
+      <c r="H66" t="s">
+        <v>35</v>
+      </c>
+      <c r="I66">
+        <v>8</v>
+      </c>
+      <c r="J66" t="s">
+        <v>36</v>
+      </c>
+      <c r="K66">
+        <v>215</v>
+      </c>
+      <c r="L66">
+        <v>1.2651159999999999</v>
+      </c>
+      <c r="M66">
+        <v>33.25</v>
+      </c>
+      <c r="N66" t="s">
+        <v>44</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>266</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>67</v>
+      </c>
+      <c r="R66">
+        <v>272</v>
+      </c>
+      <c r="S66">
+        <v>977.94117600000004</v>
+      </c>
+      <c r="T66">
+        <v>8</v>
+      </c>
+      <c r="V66">
+        <v>33.25</v>
+      </c>
+      <c r="W66">
+        <v>2.941176</v>
+      </c>
+      <c r="X66">
+        <v>8</v>
+      </c>
+      <c r="Y66">
+        <v>2.941176</v>
+      </c>
+      <c r="Z66">
+        <v>33.25</v>
+      </c>
+      <c r="AA66">
+        <v>7</v>
+      </c>
+      <c r="AB66">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>28</v>
+      </c>
+      <c r="B67" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" t="s">
+        <v>31</v>
+      </c>
+      <c r="E67" t="s">
+        <v>42</v>
+      </c>
+      <c r="F67" t="s">
+        <v>33</v>
+      </c>
+      <c r="G67" t="s">
+        <v>50</v>
+      </c>
+      <c r="H67" t="s">
+        <v>35</v>
+      </c>
+      <c r="I67">
+        <v>120</v>
+      </c>
+      <c r="J67" t="s">
+        <v>36</v>
+      </c>
+      <c r="K67">
+        <v>2980</v>
+      </c>
+      <c r="L67">
+        <v>1.431208</v>
+      </c>
+      <c r="M67">
+        <v>41.024999999999999</v>
+      </c>
+      <c r="N67" t="s">
+        <v>44</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>4923</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>67</v>
+      </c>
+      <c r="R67">
+        <v>4265</v>
+      </c>
+      <c r="S67">
+        <v>1154.2790150000001</v>
+      </c>
+      <c r="T67">
+        <v>120</v>
+      </c>
+      <c r="V67">
+        <v>41.024999999999999</v>
+      </c>
+      <c r="W67">
+        <v>2.813599</v>
+      </c>
+      <c r="X67">
+        <v>131</v>
+      </c>
+      <c r="Y67">
+        <v>3.0715119999999998</v>
+      </c>
+      <c r="Z67">
+        <v>37.580153000000003</v>
+      </c>
+      <c r="AA67">
+        <v>100</v>
+      </c>
+      <c r="AB67">
+        <v>49.23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>28</v>
+      </c>
+      <c r="B68" t="s">
+        <v>29</v>
+      </c>
+      <c r="C68" t="s">
+        <v>66</v>
+      </c>
+      <c r="D68" t="s">
+        <v>31</v>
+      </c>
+      <c r="E68" t="s">
+        <v>32</v>
+      </c>
+      <c r="F68" t="s">
+        <v>33</v>
+      </c>
+      <c r="G68" t="s">
+        <v>34</v>
+      </c>
+      <c r="H68" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68">
+        <v>19</v>
+      </c>
+      <c r="J68" t="s">
+        <v>36</v>
+      </c>
+      <c r="K68">
+        <v>720</v>
+      </c>
+      <c r="L68">
+        <v>1.3374999999999999</v>
+      </c>
+      <c r="M68">
+        <v>43.473684210000002</v>
+      </c>
+      <c r="N68" t="s">
+        <v>44</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>826</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>56</v>
+      </c>
+      <c r="R68">
+        <v>963</v>
+      </c>
+      <c r="S68">
+        <v>857.73624099999995</v>
+      </c>
+      <c r="T68">
+        <v>19</v>
+      </c>
+      <c r="V68">
+        <v>43.473683999999999</v>
+      </c>
+      <c r="W68">
+        <v>1.973001</v>
+      </c>
+      <c r="X68">
+        <v>24</v>
+      </c>
+      <c r="Y68">
+        <v>2.4922119999999999</v>
+      </c>
+      <c r="Z68">
+        <v>34.416666999999997</v>
+      </c>
+      <c r="AA68">
+        <v>16</v>
+      </c>
+      <c r="AB68">
+        <v>51.625</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>28</v>
+      </c>
+      <c r="B69" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" t="s">
+        <v>66</v>
+      </c>
+      <c r="D69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E69" t="s">
+        <v>39</v>
+      </c>
+      <c r="F69" t="s">
+        <v>33</v>
+      </c>
+      <c r="G69" t="s">
+        <v>34</v>
+      </c>
+      <c r="H69" t="s">
+        <v>35</v>
+      </c>
+      <c r="I69">
+        <v>9</v>
+      </c>
+      <c r="J69" t="s">
+        <v>36</v>
+      </c>
+      <c r="K69">
+        <v>245</v>
+      </c>
+      <c r="L69">
+        <v>1.2448980000000001</v>
+      </c>
+      <c r="M69">
+        <v>16.88888889</v>
+      </c>
+      <c r="N69" t="s">
+        <v>44</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>152</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>56</v>
+      </c>
+      <c r="R69">
+        <v>305</v>
+      </c>
+      <c r="S69">
+        <v>498.36065600000001</v>
+      </c>
+      <c r="T69">
+        <v>9</v>
+      </c>
+      <c r="V69">
+        <v>16.888888999999999</v>
+      </c>
+      <c r="W69">
+        <v>2.9508200000000002</v>
+      </c>
+      <c r="X69">
+        <v>10</v>
+      </c>
+      <c r="Y69">
+        <v>3.278689</v>
+      </c>
+      <c r="Z69">
+        <v>15.2</v>
+      </c>
+      <c r="AA69">
+        <v>6</v>
+      </c>
+      <c r="AB69">
+        <v>25.333333</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>28</v>
+      </c>
+      <c r="B70" t="s">
+        <v>29</v>
+      </c>
+      <c r="C70" t="s">
+        <v>66</v>
+      </c>
+      <c r="D70" t="s">
+        <v>31</v>
+      </c>
+      <c r="E70" t="s">
+        <v>40</v>
+      </c>
+      <c r="F70" t="s">
+        <v>33</v>
+      </c>
+      <c r="G70" t="s">
+        <v>34</v>
+      </c>
+      <c r="H70" t="s">
+        <v>35</v>
+      </c>
+      <c r="K70">
+        <v>38</v>
+      </c>
+      <c r="L70">
+        <v>1.3157890000000001</v>
+      </c>
+      <c r="N70" t="s">
+        <v>44</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>13</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>56</v>
+      </c>
+      <c r="R70">
+        <v>50</v>
+      </c>
+      <c r="S70">
+        <v>260</v>
+      </c>
+      <c r="X70">
+        <v>0</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>28</v>
+      </c>
+      <c r="B71" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71" t="s">
+        <v>66</v>
+      </c>
+      <c r="D71" t="s">
+        <v>31</v>
+      </c>
+      <c r="E71" t="s">
+        <v>41</v>
+      </c>
+      <c r="F71" t="s">
+        <v>33</v>
+      </c>
+      <c r="G71" t="s">
+        <v>34</v>
+      </c>
+      <c r="H71" t="s">
+        <v>35</v>
+      </c>
+      <c r="I71">
+        <v>40</v>
+      </c>
+      <c r="J71" t="s">
+        <v>36</v>
+      </c>
+      <c r="K71">
+        <v>630</v>
+      </c>
+      <c r="L71">
+        <v>1.2746029999999999</v>
+      </c>
+      <c r="M71">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="N71" t="s">
+        <v>44</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>744</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>56</v>
+      </c>
+      <c r="R71">
+        <v>803</v>
+      </c>
+      <c r="S71">
+        <v>926.52552900000001</v>
+      </c>
+      <c r="T71">
+        <v>40</v>
+      </c>
+      <c r="V71">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="W71">
+        <v>4.9813200000000002</v>
+      </c>
+      <c r="X71">
+        <v>40</v>
+      </c>
+      <c r="Y71">
+        <v>4.9813200000000002</v>
+      </c>
+      <c r="Z71">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="AA71">
+        <v>33</v>
+      </c>
+      <c r="AB71">
+        <v>22.545455</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>28</v>
+      </c>
+      <c r="B72" t="s">
+        <v>29</v>
+      </c>
+      <c r="C72" t="s">
+        <v>66</v>
+      </c>
+      <c r="D72" t="s">
+        <v>31</v>
+      </c>
+      <c r="E72" t="s">
+        <v>42</v>
+      </c>
+      <c r="F72" t="s">
+        <v>33</v>
+      </c>
+      <c r="G72" t="s">
+        <v>34</v>
+      </c>
+      <c r="H72" t="s">
+        <v>35</v>
+      </c>
+      <c r="I72">
+        <v>150</v>
+      </c>
+      <c r="J72" t="s">
+        <v>36</v>
+      </c>
+      <c r="K72">
+        <v>2623</v>
+      </c>
+      <c r="L72">
+        <v>1.3495999999999999</v>
+      </c>
+      <c r="M72">
+        <v>28.95333333</v>
+      </c>
+      <c r="N72" t="s">
+        <v>44</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>4343</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>56</v>
+      </c>
+      <c r="R72">
+        <v>3540</v>
+      </c>
+      <c r="S72">
+        <v>1226.8361580000001</v>
+      </c>
+      <c r="T72">
+        <v>150</v>
+      </c>
+      <c r="V72">
+        <v>28.953333000000001</v>
+      </c>
+      <c r="W72">
+        <v>4.2372880000000004</v>
+      </c>
+      <c r="X72">
+        <v>177</v>
+      </c>
+      <c r="Y72">
+        <v>5</v>
+      </c>
+      <c r="Z72">
+        <v>24.536722999999999</v>
+      </c>
+      <c r="AA72">
+        <v>120</v>
+      </c>
+      <c r="AB72">
+        <v>36.191667000000002</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>28</v>
+      </c>
+      <c r="B73" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" t="s">
+        <v>66</v>
+      </c>
+      <c r="D73" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73" t="s">
+        <v>42</v>
+      </c>
+      <c r="F73" t="s">
+        <v>59</v>
+      </c>
+      <c r="G73" t="s">
+        <v>34</v>
+      </c>
+      <c r="H73" t="s">
+        <v>35</v>
+      </c>
+      <c r="K73">
+        <v>2</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+      <c r="N73" t="s">
+        <v>44</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>56</v>
+      </c>
+      <c r="R73">
+        <v>2</v>
+      </c>
+      <c r="S73">
+        <v>500</v>
+      </c>
+      <c r="X73">
+        <v>0</v>
+      </c>
+      <c r="Y73">
+        <v>0</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>28</v>
+      </c>
+      <c r="B74" t="s">
+        <v>29</v>
+      </c>
+      <c r="C74" t="s">
+        <v>65</v>
+      </c>
+      <c r="D74" t="s">
+        <v>31</v>
+      </c>
+      <c r="E74" t="s">
+        <v>32</v>
+      </c>
+      <c r="F74" t="s">
+        <v>33</v>
+      </c>
+      <c r="G74" t="s">
+        <v>50</v>
+      </c>
+      <c r="H74" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74">
+        <v>7</v>
+      </c>
+      <c r="J74" t="s">
+        <v>36</v>
+      </c>
+      <c r="K74">
+        <v>377</v>
+      </c>
+      <c r="L74">
+        <v>1.503979</v>
+      </c>
+      <c r="M74">
+        <v>65.428571430000005</v>
+      </c>
+      <c r="N74" t="s">
+        <v>44</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>458</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>58</v>
+      </c>
+      <c r="R74">
+        <v>567</v>
+      </c>
+      <c r="S74">
+        <v>807.76014099999998</v>
+      </c>
+      <c r="T74">
+        <v>7</v>
+      </c>
+      <c r="V74">
+        <v>65.428571000000005</v>
+      </c>
+      <c r="W74">
+        <v>1.2345680000000001</v>
+      </c>
+      <c r="X74">
+        <v>11</v>
+      </c>
+      <c r="Y74">
+        <v>1.940035</v>
+      </c>
+      <c r="Z74">
+        <v>41.636364</v>
+      </c>
+      <c r="AA74">
+        <v>4</v>
+      </c>
+      <c r="AB74">
+        <v>114.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>28</v>
+      </c>
+      <c r="B75" t="s">
+        <v>29</v>
+      </c>
+      <c r="C75" t="s">
+        <v>65</v>
+      </c>
+      <c r="D75" t="s">
+        <v>31</v>
+      </c>
+      <c r="E75" t="s">
+        <v>39</v>
+      </c>
+      <c r="F75" t="s">
+        <v>33</v>
+      </c>
+      <c r="G75" t="s">
+        <v>50</v>
+      </c>
+      <c r="H75" t="s">
+        <v>35</v>
+      </c>
+      <c r="K75">
+        <v>38</v>
+      </c>
+      <c r="L75">
+        <v>1.3947369999999999</v>
+      </c>
+      <c r="N75" t="s">
+        <v>44</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>20</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>58</v>
+      </c>
+      <c r="R75">
+        <v>53</v>
+      </c>
+      <c r="S75">
+        <v>377.35849100000001</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+      <c r="Y75">
+        <v>0</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>28</v>
+      </c>
+      <c r="B76" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" t="s">
+        <v>65</v>
+      </c>
+      <c r="D76" t="s">
+        <v>31</v>
+      </c>
+      <c r="E76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F76" t="s">
+        <v>33</v>
+      </c>
+      <c r="G76" t="s">
+        <v>50</v>
+      </c>
+      <c r="H76" t="s">
+        <v>35</v>
+      </c>
+      <c r="K76">
+        <v>13</v>
+      </c>
+      <c r="L76">
+        <v>1.0769230000000001</v>
+      </c>
+      <c r="N76" t="s">
+        <v>44</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>58</v>
+      </c>
+      <c r="R76">
+        <v>14</v>
+      </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
+      <c r="X76">
+        <v>0</v>
+      </c>
+      <c r="Y76">
+        <v>0</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>28</v>
+      </c>
+      <c r="B77" t="s">
+        <v>29</v>
+      </c>
+      <c r="C77" t="s">
+        <v>65</v>
+      </c>
+      <c r="D77" t="s">
+        <v>31</v>
+      </c>
+      <c r="E77" t="s">
+        <v>41</v>
+      </c>
+      <c r="F77" t="s">
+        <v>33</v>
+      </c>
+      <c r="G77" t="s">
+        <v>50</v>
+      </c>
+      <c r="H77" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77">
+        <v>3</v>
+      </c>
+      <c r="J77" t="s">
+        <v>36</v>
+      </c>
+      <c r="K77">
+        <v>211</v>
+      </c>
+      <c r="L77">
+        <v>1.402844</v>
+      </c>
+      <c r="M77">
+        <v>49.333333330000002</v>
+      </c>
+      <c r="N77" t="s">
+        <v>44</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>148</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>58</v>
+      </c>
+      <c r="R77">
+        <v>296</v>
+      </c>
+      <c r="S77">
+        <v>500</v>
+      </c>
+      <c r="T77">
+        <v>3</v>
+      </c>
+      <c r="V77">
+        <v>49.333333000000003</v>
+      </c>
+      <c r="W77">
+        <v>1.013514</v>
+      </c>
+      <c r="X77">
+        <v>5</v>
+      </c>
+      <c r="Y77">
+        <v>1.6891890000000001</v>
+      </c>
+      <c r="Z77">
+        <v>29.6</v>
+      </c>
+      <c r="AA77">
+        <v>4</v>
+      </c>
+      <c r="AB77">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>28</v>
+      </c>
+      <c r="B78" t="s">
+        <v>29</v>
+      </c>
+      <c r="C78" t="s">
+        <v>65</v>
+      </c>
+      <c r="D78" t="s">
+        <v>31</v>
+      </c>
+      <c r="E78" t="s">
+        <v>42</v>
+      </c>
+      <c r="F78" t="s">
+        <v>33</v>
+      </c>
+      <c r="G78" t="s">
+        <v>50</v>
+      </c>
+      <c r="H78" t="s">
+        <v>35</v>
+      </c>
+      <c r="I78">
+        <v>103</v>
+      </c>
+      <c r="J78" t="s">
+        <v>36</v>
+      </c>
+      <c r="K78">
+        <v>3789</v>
+      </c>
+      <c r="L78">
+        <v>2.6014780000000002</v>
+      </c>
+      <c r="M78">
+        <v>47.339805830000003</v>
+      </c>
+      <c r="N78" t="s">
+        <v>44</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>4876</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>58</v>
+      </c>
+      <c r="R78">
+        <v>9857</v>
+      </c>
+      <c r="S78">
+        <v>494.67383599999999</v>
+      </c>
+      <c r="T78">
+        <v>103</v>
+      </c>
+      <c r="V78">
+        <v>47.339806000000003</v>
+      </c>
+      <c r="W78">
+        <v>1.044943</v>
+      </c>
+      <c r="X78">
+        <v>124</v>
+      </c>
+      <c r="Y78">
+        <v>1.257989</v>
+      </c>
+      <c r="Z78">
+        <v>39.322581</v>
+      </c>
+      <c r="AA78">
+        <v>80</v>
+      </c>
+      <c r="AB78">
+        <v>60.95</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>28</v>
+      </c>
+      <c r="B79" t="s">
+        <v>29</v>
+      </c>
+      <c r="C79" t="s">
+        <v>64</v>
+      </c>
+      <c r="D79" t="s">
+        <v>31</v>
+      </c>
+      <c r="E79" t="s">
+        <v>32</v>
+      </c>
+      <c r="F79" t="s">
+        <v>33</v>
+      </c>
+      <c r="G79" t="s">
+        <v>50</v>
+      </c>
+      <c r="H79" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79">
+        <v>60</v>
+      </c>
+      <c r="J79" t="s">
+        <v>36</v>
+      </c>
+      <c r="K79">
+        <v>1867</v>
+      </c>
+      <c r="L79">
+        <v>1.3438669999999999</v>
+      </c>
+      <c r="M79">
+        <v>31.18333333</v>
+      </c>
+      <c r="N79" t="s">
+        <v>44</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>1871</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>63</v>
+      </c>
+      <c r="R79">
+        <v>2509</v>
+      </c>
+      <c r="S79">
+        <v>745.71542399999998</v>
+      </c>
+      <c r="T79">
+        <v>60</v>
+      </c>
+      <c r="V79">
+        <v>31.183333000000001</v>
+      </c>
+      <c r="W79">
+        <v>2.391391</v>
+      </c>
+      <c r="X79">
+        <v>66</v>
+      </c>
+      <c r="Y79">
+        <v>2.6305299999999998</v>
+      </c>
+      <c r="Z79">
+        <v>28.348485</v>
+      </c>
+      <c r="AA79">
+        <v>51</v>
+      </c>
+      <c r="AB79">
+        <v>36.686275000000002</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>28</v>
+      </c>
+      <c r="B80" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" t="s">
+        <v>64</v>
+      </c>
+      <c r="D80" t="s">
+        <v>31</v>
+      </c>
+      <c r="E80" t="s">
+        <v>32</v>
+      </c>
+      <c r="F80" t="s">
+        <v>59</v>
+      </c>
+      <c r="G80" t="s">
+        <v>50</v>
+      </c>
+      <c r="H80" t="s">
+        <v>35</v>
+      </c>
+      <c r="K80">
+        <v>3</v>
+      </c>
+      <c r="L80">
+        <v>1</v>
+      </c>
+      <c r="N80" t="s">
+        <v>44</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>2</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>63</v>
+      </c>
+      <c r="R80">
+        <v>3</v>
+      </c>
+      <c r="S80">
+        <v>666.66666699999996</v>
+      </c>
+      <c r="X80">
+        <v>0</v>
+      </c>
+      <c r="Y80">
+        <v>0</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>28</v>
+      </c>
+      <c r="B81" t="s">
+        <v>29</v>
+      </c>
+      <c r="C81" t="s">
+        <v>64</v>
+      </c>
+      <c r="D81" t="s">
+        <v>31</v>
+      </c>
+      <c r="E81" t="s">
+        <v>39</v>
+      </c>
+      <c r="F81" t="s">
+        <v>33</v>
+      </c>
+      <c r="G81" t="s">
+        <v>50</v>
+      </c>
+      <c r="H81" t="s">
+        <v>35</v>
+      </c>
+      <c r="I81">
+        <v>5</v>
+      </c>
+      <c r="J81" t="s">
+        <v>36</v>
+      </c>
+      <c r="K81">
+        <v>305</v>
+      </c>
+      <c r="L81">
+        <v>1.2983610000000001</v>
+      </c>
+      <c r="M81">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="N81" t="s">
+        <v>44</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>199</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>63</v>
+      </c>
+      <c r="R81">
+        <v>396</v>
+      </c>
+      <c r="S81">
+        <v>502.52525300000002</v>
+      </c>
+      <c r="T81">
+        <v>5</v>
+      </c>
+      <c r="V81">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="W81">
+        <v>1.262626</v>
+      </c>
+      <c r="X81">
+        <v>6</v>
+      </c>
+      <c r="Y81">
+        <v>1.5151520000000001</v>
+      </c>
+      <c r="Z81">
+        <v>33.166666999999997</v>
+      </c>
+      <c r="AA81">
+        <v>5</v>
+      </c>
+      <c r="AB81">
+        <v>39.799999999999997</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>28</v>
+      </c>
+      <c r="B82" t="s">
+        <v>29</v>
+      </c>
+      <c r="C82" t="s">
+        <v>64</v>
+      </c>
+      <c r="D82" t="s">
+        <v>31</v>
+      </c>
+      <c r="E82" t="s">
+        <v>40</v>
+      </c>
+      <c r="F82" t="s">
+        <v>33</v>
+      </c>
+      <c r="G82" t="s">
+        <v>50</v>
+      </c>
+      <c r="H82" t="s">
+        <v>35</v>
+      </c>
+      <c r="K82">
+        <v>32</v>
+      </c>
+      <c r="L82">
+        <v>1.125</v>
+      </c>
+      <c r="N82" t="s">
+        <v>44</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>8</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>63</v>
+      </c>
+      <c r="R82">
+        <v>36</v>
+      </c>
+      <c r="S82">
+        <v>222.22222199999999</v>
+      </c>
+      <c r="X82">
+        <v>0</v>
+      </c>
+      <c r="Y82">
+        <v>0</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>28</v>
+      </c>
+      <c r="B83" t="s">
+        <v>29</v>
+      </c>
+      <c r="C83" t="s">
+        <v>64</v>
+      </c>
+      <c r="D83" t="s">
+        <v>31</v>
+      </c>
+      <c r="E83" t="s">
+        <v>41</v>
+      </c>
+      <c r="F83" t="s">
+        <v>33</v>
+      </c>
+      <c r="G83" t="s">
+        <v>50</v>
+      </c>
+      <c r="H83" t="s">
+        <v>35</v>
+      </c>
+      <c r="I83">
+        <v>23</v>
+      </c>
+      <c r="J83" t="s">
+        <v>36</v>
+      </c>
+      <c r="K83">
+        <v>822</v>
+      </c>
+      <c r="L83">
+        <v>1.225061</v>
+      </c>
+      <c r="M83">
+        <v>32.173913040000002</v>
+      </c>
+      <c r="N83" t="s">
+        <v>44</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>740</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>63</v>
+      </c>
+      <c r="R83">
+        <v>1007</v>
+      </c>
+      <c r="S83">
+        <v>734.85600799999997</v>
+      </c>
+      <c r="T83">
+        <v>23</v>
+      </c>
+      <c r="V83">
+        <v>32.173912999999999</v>
+      </c>
+      <c r="W83">
+        <v>2.2840120000000002</v>
+      </c>
+      <c r="X83">
+        <v>25</v>
+      </c>
+      <c r="Y83">
+        <v>2.4826220000000001</v>
+      </c>
+      <c r="Z83">
+        <v>29.6</v>
+      </c>
+      <c r="AA83">
+        <v>19</v>
+      </c>
+      <c r="AB83">
+        <v>38.947367999999997</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>28</v>
+      </c>
+      <c r="B84" t="s">
+        <v>29</v>
+      </c>
+      <c r="C84" t="s">
+        <v>64</v>
+      </c>
+      <c r="D84" t="s">
+        <v>31</v>
+      </c>
+      <c r="E84" t="s">
+        <v>42</v>
+      </c>
+      <c r="F84" t="s">
+        <v>33</v>
+      </c>
+      <c r="G84" t="s">
+        <v>50</v>
+      </c>
+      <c r="H84" t="s">
+        <v>35</v>
+      </c>
+      <c r="I84">
+        <v>90</v>
+      </c>
+      <c r="J84" t="s">
+        <v>36</v>
+      </c>
+      <c r="K84">
+        <v>2066</v>
+      </c>
+      <c r="L84">
+        <v>1.3954500000000001</v>
+      </c>
+      <c r="M84">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="N84" t="s">
+        <v>44</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>2943</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>63</v>
+      </c>
+      <c r="R84">
+        <v>2883</v>
+      </c>
+      <c r="S84">
+        <v>1020.811655</v>
+      </c>
+      <c r="T84">
+        <v>90</v>
+      </c>
+      <c r="V84">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="W84">
+        <v>3.1217480000000002</v>
+      </c>
+      <c r="X84">
+        <v>100</v>
+      </c>
+      <c r="Y84">
+        <v>3.4686089999999998</v>
+      </c>
+      <c r="Z84">
+        <v>29.43</v>
+      </c>
+      <c r="AA84">
+        <v>70</v>
+      </c>
+      <c r="AB84">
+        <v>42.042856999999998</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>28</v>
+      </c>
+      <c r="B85" t="s">
+        <v>29</v>
+      </c>
+      <c r="C85" t="s">
+        <v>64</v>
+      </c>
+      <c r="D85" t="s">
+        <v>31</v>
+      </c>
+      <c r="E85" t="s">
+        <v>42</v>
+      </c>
+      <c r="F85" t="s">
+        <v>59</v>
+      </c>
+      <c r="G85" t="s">
+        <v>50</v>
+      </c>
+      <c r="H85" t="s">
+        <v>35</v>
+      </c>
+      <c r="K85">
+        <v>2</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="N85" t="s">
+        <v>44</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>1</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>63</v>
+      </c>
+      <c r="R85">
+        <v>2</v>
+      </c>
+      <c r="S85">
+        <v>500</v>
+      </c>
+      <c r="X85">
+        <v>0</v>
+      </c>
+      <c r="Y85">
+        <v>0</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>28</v>
+      </c>
+      <c r="B86" t="s">
+        <v>29</v>
+      </c>
+      <c r="C86" t="s">
+        <v>62</v>
+      </c>
+      <c r="D86" t="s">
+        <v>31</v>
+      </c>
+      <c r="E86" t="s">
+        <v>32</v>
+      </c>
+      <c r="F86" t="s">
+        <v>33</v>
+      </c>
+      <c r="G86" t="s">
+        <v>34</v>
+      </c>
+      <c r="H86" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86">
+        <v>153</v>
+      </c>
+      <c r="J86" t="s">
+        <v>36</v>
+      </c>
+      <c r="K86">
+        <v>3510</v>
+      </c>
+      <c r="L86">
+        <v>1.7273499999999999</v>
+      </c>
+      <c r="M86">
+        <v>23.967320260000001</v>
+      </c>
+      <c r="N86" t="s">
+        <v>44</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>3667</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>56</v>
+      </c>
+      <c r="R86">
+        <v>6063</v>
+      </c>
+      <c r="S86">
+        <v>604.81609800000001</v>
+      </c>
+      <c r="T86">
+        <v>153</v>
+      </c>
+      <c r="V86">
+        <v>23.967320000000001</v>
+      </c>
+      <c r="W86">
+        <v>2.5235029999999998</v>
+      </c>
+      <c r="X86">
+        <v>166</v>
+      </c>
+      <c r="Y86">
+        <v>2.7379190000000002</v>
+      </c>
+      <c r="Z86">
+        <v>22.090361000000001</v>
+      </c>
+      <c r="AA86">
+        <v>122</v>
+      </c>
+      <c r="AB86">
+        <v>30.057376999999999</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>28</v>
+      </c>
+      <c r="B87" t="s">
+        <v>29</v>
+      </c>
+      <c r="C87" t="s">
+        <v>62</v>
+      </c>
+      <c r="D87" t="s">
+        <v>31</v>
+      </c>
+      <c r="E87" t="s">
+        <v>32</v>
+      </c>
+      <c r="F87" t="s">
+        <v>59</v>
+      </c>
+      <c r="G87" t="s">
+        <v>34</v>
+      </c>
+      <c r="H87" t="s">
+        <v>35</v>
+      </c>
+      <c r="K87">
+        <v>2</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="N87" t="s">
+        <v>44</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>56</v>
+      </c>
+      <c r="R87">
+        <v>2</v>
+      </c>
+      <c r="S87">
+        <v>0</v>
+      </c>
+      <c r="X87">
+        <v>0</v>
+      </c>
+      <c r="Y87">
+        <v>0</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>28</v>
+      </c>
+      <c r="B88" t="s">
+        <v>29</v>
+      </c>
+      <c r="C88" t="s">
+        <v>62</v>
+      </c>
+      <c r="D88" t="s">
+        <v>31</v>
+      </c>
+      <c r="E88" t="s">
+        <v>39</v>
+      </c>
+      <c r="F88" t="s">
+        <v>33</v>
+      </c>
+      <c r="G88" t="s">
+        <v>34</v>
+      </c>
+      <c r="H88" t="s">
+        <v>35</v>
+      </c>
+      <c r="I88">
+        <v>10</v>
+      </c>
+      <c r="J88" t="s">
+        <v>36</v>
+      </c>
+      <c r="K88">
+        <v>538</v>
+      </c>
+      <c r="L88">
+        <v>1.4107810000000001</v>
+      </c>
+      <c r="M88">
+        <v>23.3</v>
+      </c>
+      <c r="N88" t="s">
+        <v>44</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>233</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>56</v>
+      </c>
+      <c r="R88">
+        <v>759</v>
+      </c>
+      <c r="S88">
+        <v>306.98287199999999</v>
+      </c>
+      <c r="T88">
+        <v>10</v>
+      </c>
+      <c r="V88">
+        <v>23.3</v>
+      </c>
+      <c r="W88">
+        <v>1.317523</v>
+      </c>
+      <c r="X88">
+        <v>9</v>
+      </c>
+      <c r="Y88">
+        <v>1.1857709999999999</v>
+      </c>
+      <c r="Z88">
+        <v>25.888888999999999</v>
+      </c>
+      <c r="AA88">
+        <v>5</v>
+      </c>
+      <c r="AB88">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>28</v>
+      </c>
+      <c r="B89" t="s">
+        <v>29</v>
+      </c>
+      <c r="C89" t="s">
+        <v>62</v>
+      </c>
+      <c r="D89" t="s">
+        <v>31</v>
+      </c>
+      <c r="E89" t="s">
+        <v>40</v>
+      </c>
+      <c r="F89" t="s">
+        <v>33</v>
+      </c>
+      <c r="G89" t="s">
+        <v>34</v>
+      </c>
+      <c r="H89" t="s">
+        <v>35</v>
+      </c>
+      <c r="K89">
+        <v>161</v>
+      </c>
+      <c r="L89">
+        <v>1.2422359999999999</v>
+      </c>
+      <c r="N89" t="s">
+        <v>44</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>9</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>56</v>
+      </c>
+      <c r="R89">
+        <v>200</v>
+      </c>
+      <c r="S89">
+        <v>45</v>
+      </c>
+      <c r="X89">
+        <v>0</v>
+      </c>
+      <c r="Y89">
+        <v>0</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>28</v>
+      </c>
+      <c r="B90" t="s">
+        <v>29</v>
+      </c>
+      <c r="C90" t="s">
+        <v>62</v>
+      </c>
+      <c r="D90" t="s">
+        <v>31</v>
+      </c>
+      <c r="E90" t="s">
+        <v>41</v>
+      </c>
+      <c r="F90" t="s">
+        <v>33</v>
+      </c>
+      <c r="G90" t="s">
+        <v>34</v>
+      </c>
+      <c r="H90" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90">
+        <v>19</v>
+      </c>
+      <c r="J90" t="s">
+        <v>36</v>
+      </c>
+      <c r="K90">
+        <v>591</v>
+      </c>
+      <c r="L90">
+        <v>1.2707280000000001</v>
+      </c>
+      <c r="M90">
+        <v>22.263157889999999</v>
+      </c>
+      <c r="N90" t="s">
+        <v>44</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>423</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>56</v>
+      </c>
+      <c r="R90">
+        <v>751</v>
+      </c>
+      <c r="S90">
+        <v>563.24900100000002</v>
+      </c>
+      <c r="T90">
+        <v>19</v>
+      </c>
+      <c r="V90">
+        <v>22.263158000000001</v>
+      </c>
+      <c r="W90">
+        <v>2.52996</v>
+      </c>
+      <c r="X90">
+        <v>28</v>
+      </c>
+      <c r="Y90">
+        <v>3.7283620000000002</v>
+      </c>
+      <c r="Z90">
+        <v>15.107143000000001</v>
+      </c>
+      <c r="AA90">
+        <v>18</v>
+      </c>
+      <c r="AB90">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>28</v>
+      </c>
+      <c r="B91" t="s">
+        <v>29</v>
+      </c>
+      <c r="C91" t="s">
+        <v>62</v>
+      </c>
+      <c r="D91" t="s">
+        <v>31</v>
+      </c>
+      <c r="E91" t="s">
+        <v>42</v>
+      </c>
+      <c r="F91" t="s">
+        <v>33</v>
+      </c>
+      <c r="G91" t="s">
+        <v>34</v>
+      </c>
+      <c r="H91" t="s">
+        <v>35</v>
+      </c>
+      <c r="I91">
+        <v>243</v>
+      </c>
+      <c r="J91" t="s">
+        <v>36</v>
+      </c>
+      <c r="K91">
+        <v>5933</v>
+      </c>
+      <c r="L91">
+        <v>1.5926180000000001</v>
+      </c>
+      <c r="M91">
+        <v>26.238683129999998</v>
+      </c>
+      <c r="N91" t="s">
+        <v>44</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>6376</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>56</v>
+      </c>
+      <c r="R91">
+        <v>9449</v>
+      </c>
+      <c r="S91">
+        <v>674.78039999999999</v>
+      </c>
+      <c r="T91">
+        <v>243</v>
+      </c>
+      <c r="V91">
+        <v>26.238683000000002</v>
+      </c>
+      <c r="W91">
+        <v>2.571701</v>
+      </c>
+      <c r="X91">
+        <v>290</v>
+      </c>
+      <c r="Y91">
+        <v>3.0691079999999999</v>
+      </c>
+      <c r="Z91">
+        <v>21.986207</v>
+      </c>
+      <c r="AA91">
+        <v>199</v>
+      </c>
+      <c r="AB91">
+        <v>32.040201000000003</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>28</v>
+      </c>
+      <c r="B92" t="s">
+        <v>29</v>
+      </c>
+      <c r="C92" t="s">
+        <v>62</v>
+      </c>
+      <c r="D92" t="s">
+        <v>31</v>
+      </c>
+      <c r="E92" t="s">
+        <v>42</v>
+      </c>
+      <c r="F92" t="s">
+        <v>59</v>
+      </c>
+      <c r="G92" t="s">
+        <v>34</v>
+      </c>
+      <c r="H92" t="s">
+        <v>35</v>
+      </c>
+      <c r="K92">
+        <v>6</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="N92" t="s">
+        <v>44</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>1</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>56</v>
+      </c>
+      <c r="R92">
+        <v>6</v>
+      </c>
+      <c r="S92">
+        <v>166.66666699999999</v>
+      </c>
+      <c r="X92">
+        <v>0</v>
+      </c>
+      <c r="Y92">
+        <v>0</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>28</v>
+      </c>
+      <c r="B93" t="s">
+        <v>29</v>
+      </c>
+      <c r="C93" t="s">
+        <v>61</v>
+      </c>
+      <c r="D93" t="s">
+        <v>31</v>
+      </c>
+      <c r="E93" t="s">
+        <v>32</v>
+      </c>
+      <c r="F93" t="s">
+        <v>33</v>
+      </c>
+      <c r="G93" t="s">
+        <v>34</v>
+      </c>
+      <c r="H93" t="s">
+        <v>35</v>
+      </c>
+      <c r="I93">
+        <v>43</v>
+      </c>
+      <c r="J93" t="s">
+        <v>36</v>
+      </c>
+      <c r="K93">
+        <v>1673</v>
+      </c>
+      <c r="L93">
+        <v>1.557083</v>
+      </c>
+      <c r="M93">
+        <v>41.255813949999997</v>
+      </c>
+      <c r="N93" t="s">
+        <v>44</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>1774</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>56</v>
+      </c>
+      <c r="R93">
+        <v>2605</v>
+      </c>
+      <c r="S93">
+        <v>680.99808099999996</v>
+      </c>
+      <c r="T93">
+        <v>43</v>
+      </c>
+      <c r="V93">
+        <v>41.255814000000001</v>
+      </c>
+      <c r="W93">
+        <v>1.6506719999999999</v>
+      </c>
+      <c r="X93">
+        <v>46</v>
+      </c>
+      <c r="Y93">
+        <v>1.765835</v>
+      </c>
+      <c r="Z93">
+        <v>38.565216999999997</v>
+      </c>
+      <c r="AA93">
+        <v>23</v>
+      </c>
+      <c r="AB93">
+        <v>77.130435000000006</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>28</v>
+      </c>
+      <c r="B94" t="s">
+        <v>29</v>
+      </c>
+      <c r="C94" t="s">
+        <v>61</v>
+      </c>
+      <c r="D94" t="s">
+        <v>31</v>
+      </c>
+      <c r="E94" t="s">
+        <v>39</v>
+      </c>
+      <c r="F94" t="s">
+        <v>33</v>
+      </c>
+      <c r="G94" t="s">
+        <v>34</v>
+      </c>
+      <c r="H94" t="s">
+        <v>35</v>
+      </c>
+      <c r="I94">
+        <v>8</v>
+      </c>
+      <c r="J94" t="s">
+        <v>36</v>
+      </c>
+      <c r="K94">
+        <v>556</v>
+      </c>
+      <c r="L94">
+        <v>1.3273379999999999</v>
+      </c>
+      <c r="M94">
+        <v>36.875</v>
+      </c>
+      <c r="N94" t="s">
+        <v>44</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>295</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>56</v>
+      </c>
+      <c r="R94">
+        <v>738</v>
+      </c>
+      <c r="S94">
+        <v>399.72899699999999</v>
+      </c>
+      <c r="T94">
+        <v>8</v>
+      </c>
+      <c r="V94">
+        <v>36.875</v>
+      </c>
+      <c r="W94">
+        <v>1.0840110000000001</v>
+      </c>
+      <c r="X94">
+        <v>10</v>
+      </c>
+      <c r="Y94">
+        <v>1.3550139999999999</v>
+      </c>
+      <c r="Z94">
+        <v>29.5</v>
+      </c>
+      <c r="AA94">
+        <v>4</v>
+      </c>
+      <c r="AB94">
+        <v>73.75</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>28</v>
+      </c>
+      <c r="B95" t="s">
+        <v>29</v>
+      </c>
+      <c r="C95" t="s">
+        <v>61</v>
+      </c>
+      <c r="D95" t="s">
+        <v>31</v>
+      </c>
+      <c r="E95" t="s">
+        <v>40</v>
+      </c>
+      <c r="F95" t="s">
+        <v>33</v>
+      </c>
+      <c r="G95" t="s">
+        <v>34</v>
+      </c>
+      <c r="H95" t="s">
+        <v>35</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+      <c r="J95" t="s">
+        <v>36</v>
+      </c>
+      <c r="K95">
+        <v>6</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95" t="s">
+        <v>44</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>56</v>
+      </c>
+      <c r="R95">
+        <v>6</v>
+      </c>
+      <c r="S95">
+        <v>0</v>
+      </c>
+      <c r="T95">
+        <v>1</v>
+      </c>
+      <c r="V95">
+        <v>0</v>
+      </c>
+      <c r="W95">
+        <v>16.666667</v>
+      </c>
+      <c r="X95">
+        <v>1</v>
+      </c>
+      <c r="Y95">
+        <v>16.666667</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+      <c r="AA95">
+        <v>1</v>
+      </c>
+      <c r="AB95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>28</v>
+      </c>
+      <c r="B96" t="s">
+        <v>29</v>
+      </c>
+      <c r="C96" t="s">
+        <v>61</v>
+      </c>
+      <c r="D96" t="s">
+        <v>31</v>
+      </c>
+      <c r="E96" t="s">
+        <v>41</v>
+      </c>
+      <c r="F96" t="s">
+        <v>33</v>
+      </c>
+      <c r="G96" t="s">
+        <v>34</v>
+      </c>
+      <c r="H96" t="s">
+        <v>35</v>
+      </c>
+      <c r="I96">
+        <v>18</v>
+      </c>
+      <c r="J96" t="s">
+        <v>36</v>
+      </c>
+      <c r="K96">
+        <v>341</v>
+      </c>
+      <c r="L96">
+        <v>1.340176</v>
+      </c>
+      <c r="M96">
+        <v>33</v>
+      </c>
+      <c r="N96" t="s">
+        <v>44</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>594</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>56</v>
+      </c>
+      <c r="R96">
+        <v>457</v>
+      </c>
+      <c r="S96">
+        <v>1299.7811819999999</v>
+      </c>
+      <c r="T96">
+        <v>18</v>
+      </c>
+      <c r="V96">
+        <v>33</v>
+      </c>
+      <c r="W96">
+        <v>3.9387310000000002</v>
+      </c>
+      <c r="X96">
+        <v>20</v>
+      </c>
+      <c r="Y96">
+        <v>4.3763680000000003</v>
+      </c>
+      <c r="Z96">
+        <v>29.7</v>
+      </c>
+      <c r="AA96">
+        <v>15</v>
+      </c>
+      <c r="AB96">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>28</v>
+      </c>
+      <c r="B97" t="s">
+        <v>29</v>
+      </c>
+      <c r="C97" t="s">
+        <v>61</v>
+      </c>
+      <c r="D97" t="s">
+        <v>31</v>
+      </c>
+      <c r="E97" t="s">
+        <v>42</v>
+      </c>
+      <c r="F97" t="s">
+        <v>33</v>
+      </c>
+      <c r="G97" t="s">
+        <v>34</v>
+      </c>
+      <c r="H97" t="s">
+        <v>35</v>
+      </c>
+      <c r="I97">
+        <v>92</v>
+      </c>
+      <c r="J97" t="s">
+        <v>36</v>
+      </c>
+      <c r="K97">
+        <v>2014</v>
+      </c>
+      <c r="L97">
+        <v>1.323237</v>
+      </c>
+      <c r="M97">
+        <v>39.467391300000003</v>
+      </c>
+      <c r="N97" t="s">
+        <v>44</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>3631</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>56</v>
+      </c>
+      <c r="R97">
+        <v>2665</v>
+      </c>
+      <c r="S97">
+        <v>1362.4765480000001</v>
+      </c>
+      <c r="T97">
+        <v>92</v>
+      </c>
+      <c r="V97">
+        <v>39.467390999999999</v>
+      </c>
+      <c r="W97">
+        <v>3.4521579999999998</v>
+      </c>
+      <c r="X97">
+        <v>95</v>
+      </c>
+      <c r="Y97">
+        <v>3.5647280000000001</v>
+      </c>
+      <c r="Z97">
+        <v>38.221052999999998</v>
+      </c>
+      <c r="AA97">
+        <v>55</v>
+      </c>
+      <c r="AB97">
+        <v>66.018181999999996</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>28</v>
+      </c>
+      <c r="B98" t="s">
+        <v>29</v>
+      </c>
+      <c r="C98" t="s">
+        <v>60</v>
+      </c>
+      <c r="D98" t="s">
+        <v>31</v>
+      </c>
+      <c r="E98" t="s">
+        <v>32</v>
+      </c>
+      <c r="F98" t="s">
+        <v>33</v>
+      </c>
+      <c r="G98" t="s">
+        <v>50</v>
+      </c>
+      <c r="H98" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98">
+        <v>3</v>
+      </c>
+      <c r="J98" t="s">
+        <v>36</v>
+      </c>
+      <c r="K98">
+        <v>150</v>
+      </c>
+      <c r="L98">
+        <v>1.1333329999999999</v>
+      </c>
+      <c r="M98">
+        <v>51.333333330000002</v>
+      </c>
+      <c r="N98" t="s">
+        <v>44</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>154</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>58</v>
+      </c>
+      <c r="R98">
+        <v>170</v>
+      </c>
+      <c r="S98">
+        <v>905.88235299999997</v>
+      </c>
+      <c r="T98">
+        <v>3</v>
+      </c>
+      <c r="V98">
+        <v>51.333333000000003</v>
+      </c>
+      <c r="W98">
+        <v>1.7647060000000001</v>
+      </c>
+      <c r="X98">
+        <v>6</v>
+      </c>
+      <c r="Y98">
+        <v>3.5294120000000002</v>
+      </c>
+      <c r="Z98">
+        <v>25.666667</v>
+      </c>
+      <c r="AA98">
+        <v>4</v>
+      </c>
+      <c r="AB98">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>28</v>
+      </c>
+      <c r="B99" t="s">
+        <v>29</v>
+      </c>
+      <c r="C99" t="s">
+        <v>60</v>
+      </c>
+      <c r="D99" t="s">
+        <v>31</v>
+      </c>
+      <c r="E99" t="s">
+        <v>39</v>
+      </c>
+      <c r="F99" t="s">
+        <v>33</v>
+      </c>
+      <c r="G99" t="s">
+        <v>50</v>
+      </c>
+      <c r="H99" t="s">
+        <v>35</v>
+      </c>
+      <c r="K99">
+        <v>9</v>
+      </c>
+      <c r="L99">
+        <v>1.111111</v>
+      </c>
+      <c r="N99" t="s">
+        <v>44</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>5</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>58</v>
+      </c>
+      <c r="R99">
+        <v>10</v>
+      </c>
+      <c r="S99">
+        <v>500</v>
+      </c>
+      <c r="X99">
+        <v>0</v>
+      </c>
+      <c r="Y99">
+        <v>0</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>28</v>
+      </c>
+      <c r="B100" t="s">
+        <v>29</v>
+      </c>
+      <c r="C100" t="s">
+        <v>60</v>
+      </c>
+      <c r="D100" t="s">
+        <v>31</v>
+      </c>
+      <c r="E100" t="s">
+        <v>41</v>
+      </c>
+      <c r="F100" t="s">
+        <v>33</v>
+      </c>
+      <c r="G100" t="s">
+        <v>50</v>
+      </c>
+      <c r="H100" t="s">
+        <v>35</v>
+      </c>
+      <c r="I100">
+        <v>9</v>
+      </c>
+      <c r="J100" t="s">
+        <v>36</v>
+      </c>
+      <c r="K100">
+        <v>628</v>
+      </c>
+      <c r="L100">
+        <v>1.0254779999999999</v>
+      </c>
+      <c r="M100">
+        <v>50.666666669999998</v>
+      </c>
+      <c r="N100" t="s">
+        <v>44</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>456</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>58</v>
+      </c>
+      <c r="R100">
+        <v>644</v>
+      </c>
+      <c r="S100">
+        <v>708.07453399999997</v>
+      </c>
+      <c r="T100">
+        <v>9</v>
+      </c>
+      <c r="V100">
+        <v>50.666666999999997</v>
+      </c>
+      <c r="W100">
+        <v>1.397516</v>
+      </c>
+      <c r="X100">
+        <v>13</v>
+      </c>
+      <c r="Y100">
+        <v>2.018634</v>
+      </c>
+      <c r="Z100">
+        <v>35.076923000000001</v>
+      </c>
+      <c r="AA100">
+        <v>8</v>
+      </c>
+      <c r="AB100">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="101" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>28</v>
+      </c>
+      <c r="B101" t="s">
+        <v>29</v>
+      </c>
+      <c r="C101" t="s">
+        <v>60</v>
+      </c>
+      <c r="D101" t="s">
+        <v>31</v>
+      </c>
+      <c r="E101" t="s">
+        <v>42</v>
+      </c>
+      <c r="F101" t="s">
+        <v>33</v>
+      </c>
+      <c r="G101" t="s">
+        <v>50</v>
+      </c>
+      <c r="H101" t="s">
+        <v>35</v>
+      </c>
+      <c r="I101">
+        <v>53</v>
+      </c>
+      <c r="J101" t="s">
+        <v>36</v>
+      </c>
+      <c r="K101">
+        <v>1105</v>
+      </c>
+      <c r="L101">
+        <v>1.065158</v>
+      </c>
+      <c r="M101">
+        <v>40.943396229999998</v>
+      </c>
+      <c r="N101" t="s">
+        <v>44</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>2170</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>58</v>
+      </c>
+      <c r="R101">
+        <v>1177</v>
+      </c>
+      <c r="S101">
+        <v>1843.6703480000001</v>
+      </c>
+      <c r="T101">
+        <v>53</v>
+      </c>
+      <c r="V101">
+        <v>40.943396</v>
+      </c>
+      <c r="W101">
+        <v>4.502974</v>
+      </c>
+      <c r="X101">
+        <v>58</v>
+      </c>
+      <c r="Y101">
+        <v>4.9277829999999998</v>
+      </c>
+      <c r="Z101">
+        <v>37.413792999999998</v>
+      </c>
+      <c r="AA101">
+        <v>40</v>
+      </c>
+      <c r="AB101">
+        <v>54.25</v>
+      </c>
+    </row>
+    <row r="102" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>28</v>
+      </c>
+      <c r="B102" t="s">
+        <v>29</v>
+      </c>
+      <c r="C102" t="s">
+        <v>60</v>
+      </c>
+      <c r="D102" t="s">
+        <v>31</v>
+      </c>
+      <c r="E102" t="s">
+        <v>42</v>
+      </c>
+      <c r="F102" t="s">
+        <v>59</v>
+      </c>
+      <c r="G102" t="s">
+        <v>50</v>
+      </c>
+      <c r="H102" t="s">
+        <v>35</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>1</v>
+      </c>
+      <c r="N102" t="s">
+        <v>44</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>1</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>58</v>
+      </c>
+      <c r="R102">
+        <v>1</v>
+      </c>
+      <c r="S102">
+        <v>1000</v>
+      </c>
+      <c r="X102">
+        <v>0</v>
+      </c>
+      <c r="Y102">
+        <v>0</v>
+      </c>
+      <c r="Z102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>28</v>
+      </c>
+      <c r="B103" t="s">
+        <v>29</v>
+      </c>
+      <c r="C103" t="s">
+        <v>57</v>
+      </c>
+      <c r="D103" t="s">
+        <v>31</v>
+      </c>
+      <c r="E103" t="s">
+        <v>32</v>
+      </c>
+      <c r="F103" t="s">
+        <v>33</v>
+      </c>
+      <c r="G103" t="s">
+        <v>34</v>
+      </c>
+      <c r="H103" t="s">
+        <v>35</v>
+      </c>
+      <c r="I103">
+        <v>4</v>
+      </c>
+      <c r="J103" t="s">
+        <v>36</v>
+      </c>
+      <c r="K103">
+        <v>225</v>
+      </c>
+      <c r="L103">
+        <v>1.3111109999999999</v>
+      </c>
+      <c r="M103">
+        <v>97</v>
+      </c>
+      <c r="N103" t="s">
+        <v>44</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>388</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>56</v>
+      </c>
+      <c r="R103">
+        <v>295</v>
+      </c>
+      <c r="S103">
+        <v>1315.2542370000001</v>
+      </c>
+      <c r="T103">
+        <v>4</v>
+      </c>
+      <c r="V103">
+        <v>97</v>
+      </c>
+      <c r="W103">
+        <v>1.3559319999999999</v>
+      </c>
+      <c r="X103">
+        <v>6</v>
+      </c>
+      <c r="Y103">
+        <v>2.0338980000000002</v>
+      </c>
+      <c r="Z103">
+        <v>64.666667000000004</v>
+      </c>
+      <c r="AA103">
+        <v>3</v>
+      </c>
+      <c r="AB103">
+        <v>129.33333300000001</v>
+      </c>
+    </row>
+    <row r="104" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>28</v>
+      </c>
+      <c r="B104" t="s">
+        <v>29</v>
+      </c>
+      <c r="C104" t="s">
+        <v>57</v>
+      </c>
+      <c r="D104" t="s">
+        <v>31</v>
+      </c>
+      <c r="E104" t="s">
+        <v>39</v>
+      </c>
+      <c r="F104" t="s">
+        <v>33</v>
+      </c>
+      <c r="G104" t="s">
+        <v>34</v>
+      </c>
+      <c r="H104" t="s">
+        <v>35</v>
+      </c>
+      <c r="K104">
+        <v>135</v>
+      </c>
+      <c r="L104">
+        <v>1.2370369999999999</v>
+      </c>
+      <c r="N104" t="s">
+        <v>44</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>105</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>56</v>
+      </c>
+      <c r="R104">
+        <v>167</v>
+      </c>
+      <c r="S104">
+        <v>628.74251500000003</v>
+      </c>
+      <c r="X104">
+        <v>0</v>
+      </c>
+      <c r="Y104">
+        <v>0</v>
+      </c>
+      <c r="Z104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>28</v>
+      </c>
+      <c r="B105" t="s">
+        <v>29</v>
+      </c>
+      <c r="C105" t="s">
+        <v>57</v>
+      </c>
+      <c r="D105" t="s">
+        <v>31</v>
+      </c>
+      <c r="E105" t="s">
+        <v>40</v>
+      </c>
+      <c r="F105" t="s">
+        <v>33</v>
+      </c>
+      <c r="G105" t="s">
+        <v>34</v>
+      </c>
+      <c r="H105" t="s">
+        <v>35</v>
+      </c>
+      <c r="K105">
+        <v>7</v>
+      </c>
+      <c r="L105">
+        <v>1.142857</v>
+      </c>
+      <c r="N105" t="s">
+        <v>44</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>8</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>56</v>
+      </c>
+      <c r="R105">
+        <v>8</v>
+      </c>
+      <c r="S105">
+        <v>1000</v>
+      </c>
+      <c r="X105">
+        <v>1</v>
+      </c>
+      <c r="Y105">
+        <v>12.5</v>
+      </c>
+      <c r="Z105">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>28</v>
+      </c>
+      <c r="B106" t="s">
+        <v>29</v>
+      </c>
+      <c r="C106" t="s">
+        <v>57</v>
+      </c>
+      <c r="D106" t="s">
+        <v>31</v>
+      </c>
+      <c r="E106" t="s">
+        <v>41</v>
+      </c>
+      <c r="F106" t="s">
+        <v>33</v>
+      </c>
+      <c r="G106" t="s">
+        <v>34</v>
+      </c>
+      <c r="H106" t="s">
+        <v>35</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
+      </c>
+      <c r="J106" t="s">
+        <v>36</v>
+      </c>
+      <c r="K106">
+        <v>59</v>
+      </c>
+      <c r="L106">
+        <v>1.254237</v>
+      </c>
+      <c r="M106">
+        <v>70</v>
+      </c>
+      <c r="N106" t="s">
+        <v>44</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>70</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>56</v>
+      </c>
+      <c r="R106">
+        <v>74</v>
+      </c>
+      <c r="S106">
+        <v>945.94594600000005</v>
+      </c>
+      <c r="T106">
+        <v>1</v>
+      </c>
+      <c r="V106">
+        <v>70</v>
+      </c>
+      <c r="W106">
+        <v>1.351351</v>
+      </c>
+      <c r="X106">
+        <v>1</v>
+      </c>
+      <c r="Y106">
+        <v>1.351351</v>
+      </c>
+      <c r="Z106">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="107" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>28</v>
+      </c>
+      <c r="B107" t="s">
+        <v>29</v>
+      </c>
+      <c r="C107" t="s">
+        <v>57</v>
+      </c>
+      <c r="D107" t="s">
+        <v>31</v>
+      </c>
+      <c r="E107" t="s">
+        <v>42</v>
+      </c>
+      <c r="F107" t="s">
+        <v>33</v>
+      </c>
+      <c r="G107" t="s">
+        <v>34</v>
+      </c>
+      <c r="H107" t="s">
+        <v>35</v>
+      </c>
+      <c r="I107">
+        <v>104</v>
+      </c>
+      <c r="J107" t="s">
+        <v>36</v>
+      </c>
+      <c r="K107">
+        <v>6180</v>
+      </c>
+      <c r="L107">
+        <v>1.4878640000000001</v>
+      </c>
+      <c r="M107">
+        <v>54.23076923</v>
+      </c>
+      <c r="N107" t="s">
+        <v>44</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>5640</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>56</v>
+      </c>
+      <c r="R107">
+        <v>9195</v>
+      </c>
+      <c r="S107">
+        <v>613.37683500000003</v>
+      </c>
+      <c r="T107">
+        <v>104</v>
+      </c>
+      <c r="V107">
+        <v>54.230769000000002</v>
+      </c>
+      <c r="W107">
+        <v>1.131049</v>
+      </c>
+      <c r="X107">
+        <v>114</v>
+      </c>
+      <c r="Y107">
+        <v>1.2398039999999999</v>
+      </c>
+      <c r="Z107">
+        <v>49.473683999999999</v>
+      </c>
+      <c r="AA107">
+        <v>75</v>
+      </c>
+      <c r="AB107">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>28</v>
+      </c>
+      <c r="B108" t="s">
+        <v>29</v>
+      </c>
+      <c r="C108" t="s">
+        <v>55</v>
+      </c>
+      <c r="D108" t="s">
+        <v>31</v>
+      </c>
+      <c r="E108" t="s">
+        <v>32</v>
+      </c>
+      <c r="F108" t="s">
+        <v>33</v>
+      </c>
+      <c r="G108" t="s">
+        <v>34</v>
+      </c>
+      <c r="H108" t="s">
+        <v>35</v>
+      </c>
+      <c r="I108">
+        <v>7</v>
+      </c>
+      <c r="J108" t="s">
+        <v>36</v>
+      </c>
+      <c r="K108">
+        <v>160</v>
+      </c>
+      <c r="L108">
+        <v>1.29375</v>
+      </c>
+      <c r="M108">
+        <v>30.14285714</v>
+      </c>
+      <c r="N108" t="s">
+        <v>44</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>211</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>54</v>
+      </c>
+      <c r="R108">
+        <v>207</v>
+      </c>
+      <c r="S108">
+        <v>1019.323672</v>
+      </c>
+      <c r="T108">
+        <v>7</v>
+      </c>
+      <c r="V108">
+        <v>30.142856999999999</v>
+      </c>
+      <c r="W108">
+        <v>3.381643</v>
+      </c>
+      <c r="X108">
+        <v>7</v>
+      </c>
+      <c r="Y108">
+        <v>3.381643</v>
+      </c>
+      <c r="Z108">
+        <v>30.142856999999999</v>
+      </c>
+      <c r="AA108">
+        <v>5</v>
+      </c>
+      <c r="AB108">
+        <v>42.2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>28</v>
+      </c>
+      <c r="B109" t="s">
+        <v>29</v>
+      </c>
+      <c r="C109" t="s">
+        <v>55</v>
+      </c>
+      <c r="D109" t="s">
+        <v>31</v>
+      </c>
+      <c r="E109" t="s">
+        <v>39</v>
+      </c>
+      <c r="F109" t="s">
+        <v>33</v>
+      </c>
+      <c r="G109" t="s">
+        <v>34</v>
+      </c>
+      <c r="H109" t="s">
+        <v>35</v>
+      </c>
+      <c r="I109">
+        <v>3</v>
+      </c>
+      <c r="J109" t="s">
+        <v>36</v>
+      </c>
+      <c r="K109">
+        <v>120</v>
+      </c>
+      <c r="L109">
+        <v>1.5416669999999999</v>
+      </c>
+      <c r="M109">
+        <v>37.333333330000002</v>
+      </c>
+      <c r="N109" t="s">
+        <v>44</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>112</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>54</v>
+      </c>
+      <c r="R109">
+        <v>185</v>
+      </c>
+      <c r="S109">
+        <v>605.40540499999997</v>
+      </c>
+      <c r="T109">
+        <v>3</v>
+      </c>
+      <c r="V109">
+        <v>37.333333000000003</v>
+      </c>
+      <c r="W109">
+        <v>1.6216219999999999</v>
+      </c>
+      <c r="X109">
+        <v>3</v>
+      </c>
+      <c r="Y109">
+        <v>1.6216219999999999</v>
+      </c>
+      <c r="Z109">
+        <v>37.333333000000003</v>
+      </c>
+      <c r="AA109">
+        <v>1</v>
+      </c>
+      <c r="AB109">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="110" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>28</v>
+      </c>
+      <c r="B110" t="s">
+        <v>29</v>
+      </c>
+      <c r="C110" t="s">
+        <v>55</v>
+      </c>
+      <c r="D110" t="s">
+        <v>31</v>
+      </c>
+      <c r="E110" t="s">
+        <v>40</v>
+      </c>
+      <c r="F110" t="s">
+        <v>33</v>
+      </c>
+      <c r="G110" t="s">
+        <v>34</v>
+      </c>
+      <c r="H110" t="s">
+        <v>35</v>
+      </c>
+      <c r="K110">
+        <v>3</v>
+      </c>
+      <c r="L110">
+        <v>1</v>
+      </c>
+      <c r="N110" t="s">
+        <v>44</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>54</v>
+      </c>
+      <c r="R110">
+        <v>3</v>
+      </c>
+      <c r="S110">
+        <v>0</v>
+      </c>
+      <c r="X110">
+        <v>0</v>
+      </c>
+      <c r="Y110">
+        <v>0</v>
+      </c>
+      <c r="Z110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>28</v>
+      </c>
+      <c r="B111" t="s">
+        <v>29</v>
+      </c>
+      <c r="C111" t="s">
+        <v>55</v>
+      </c>
+      <c r="D111" t="s">
+        <v>31</v>
+      </c>
+      <c r="E111" t="s">
+        <v>41</v>
+      </c>
+      <c r="F111" t="s">
+        <v>33</v>
+      </c>
+      <c r="G111" t="s">
+        <v>34</v>
+      </c>
+      <c r="H111" t="s">
+        <v>35</v>
+      </c>
+      <c r="I111">
+        <v>4</v>
+      </c>
+      <c r="J111" t="s">
+        <v>36</v>
+      </c>
+      <c r="K111">
+        <v>104</v>
+      </c>
+      <c r="L111">
+        <v>1.1826920000000001</v>
+      </c>
+      <c r="M111">
+        <v>20.75</v>
+      </c>
+      <c r="N111" t="s">
+        <v>44</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>83</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>54</v>
+      </c>
+      <c r="R111">
+        <v>123</v>
+      </c>
+      <c r="S111">
+        <v>674.79674799999998</v>
+      </c>
+      <c r="T111">
+        <v>4</v>
+      </c>
+      <c r="V111">
+        <v>20.75</v>
+      </c>
+      <c r="W111">
+        <v>3.252033</v>
+      </c>
+      <c r="X111">
+        <v>4</v>
+      </c>
+      <c r="Y111">
+        <v>3.252033</v>
+      </c>
+      <c r="Z111">
+        <v>20.75</v>
+      </c>
+      <c r="AA111">
+        <v>2</v>
+      </c>
+      <c r="AB111">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>28</v>
+      </c>
+      <c r="B112" t="s">
+        <v>29</v>
+      </c>
+      <c r="C112" t="s">
+        <v>55</v>
+      </c>
+      <c r="D112" t="s">
+        <v>31</v>
+      </c>
+      <c r="E112" t="s">
+        <v>42</v>
+      </c>
+      <c r="F112" t="s">
+        <v>33</v>
+      </c>
+      <c r="G112" t="s">
+        <v>34</v>
+      </c>
+      <c r="H112" t="s">
+        <v>35</v>
+      </c>
+      <c r="I112">
+        <v>107</v>
+      </c>
+      <c r="J112" t="s">
+        <v>36</v>
+      </c>
+      <c r="K112">
+        <v>6069</v>
+      </c>
+      <c r="L112">
+        <v>1.5033780000000001</v>
+      </c>
+      <c r="M112">
+        <v>51.925233640000002</v>
+      </c>
+      <c r="N112" t="s">
+        <v>44</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>5556</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>54</v>
+      </c>
+      <c r="R112">
+        <v>9124</v>
+      </c>
+      <c r="S112">
+        <v>608.94344599999999</v>
+      </c>
+      <c r="T112">
+        <v>107</v>
+      </c>
+      <c r="V112">
+        <v>51.925234000000003</v>
+      </c>
+      <c r="W112">
+        <v>1.172731</v>
+      </c>
+      <c r="X112">
+        <v>116</v>
+      </c>
+      <c r="Y112">
+        <v>1.2713719999999999</v>
+      </c>
+      <c r="Z112">
+        <v>47.896552</v>
+      </c>
+      <c r="AA112">
+        <v>81</v>
+      </c>
+      <c r="AB112">
+        <v>68.592592999999994</v>
+      </c>
+    </row>
+    <row r="113" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>28</v>
+      </c>
+      <c r="B113" t="s">
+        <v>29</v>
+      </c>
+      <c r="C113" t="s">
+        <v>53</v>
+      </c>
+      <c r="D113" t="s">
+        <v>31</v>
+      </c>
+      <c r="E113" t="s">
+        <v>32</v>
+      </c>
+      <c r="F113" t="s">
+        <v>33</v>
+      </c>
+      <c r="G113" t="s">
+        <v>45</v>
+      </c>
+      <c r="H113" t="s">
+        <v>35</v>
+      </c>
+      <c r="I113">
+        <v>12</v>
+      </c>
+      <c r="J113" t="s">
+        <v>36</v>
+      </c>
+      <c r="K113">
+        <v>584</v>
+      </c>
+      <c r="L113">
+        <v>1.453767</v>
+      </c>
+      <c r="M113">
+        <v>75.416666669999998</v>
+      </c>
+      <c r="N113" t="s">
+        <v>44</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>905</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>52</v>
+      </c>
+      <c r="R113">
+        <v>849</v>
+      </c>
+      <c r="S113">
+        <v>1065.959953</v>
+      </c>
+      <c r="T113">
+        <v>12</v>
+      </c>
+      <c r="V113">
+        <v>75.416667000000004</v>
+      </c>
+      <c r="W113">
+        <v>1.4134279999999999</v>
+      </c>
+      <c r="X113">
+        <v>17</v>
+      </c>
+      <c r="Y113">
+        <v>2.0023559999999998</v>
+      </c>
+      <c r="Z113">
+        <v>53.235294000000003</v>
+      </c>
+    </row>
+    <row r="114" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>28</v>
+      </c>
+      <c r="B114" t="s">
+        <v>29</v>
+      </c>
+      <c r="C114" t="s">
+        <v>53</v>
+      </c>
+      <c r="D114" t="s">
+        <v>31</v>
+      </c>
+      <c r="E114" t="s">
+        <v>39</v>
+      </c>
+      <c r="F114" t="s">
+        <v>33</v>
+      </c>
+      <c r="G114" t="s">
+        <v>45</v>
+      </c>
+      <c r="H114" t="s">
+        <v>35</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114" t="s">
+        <v>36</v>
+      </c>
+      <c r="K114">
+        <v>16</v>
+      </c>
+      <c r="L114">
+        <v>1.1875</v>
+      </c>
+      <c r="M114">
+        <v>14</v>
+      </c>
+      <c r="N114" t="s">
+        <v>44</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>14</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>52</v>
+      </c>
+      <c r="R114">
+        <v>19</v>
+      </c>
+      <c r="S114">
+        <v>736.84210499999995</v>
+      </c>
+      <c r="T114">
+        <v>1</v>
+      </c>
+      <c r="V114">
+        <v>14</v>
+      </c>
+      <c r="W114">
+        <v>5.2631579999999998</v>
+      </c>
+      <c r="X114">
+        <v>1</v>
+      </c>
+      <c r="Y114">
+        <v>5.2631579999999998</v>
+      </c>
+      <c r="Z114">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>28</v>
+      </c>
+      <c r="B115" t="s">
+        <v>29</v>
+      </c>
+      <c r="C115" t="s">
+        <v>53</v>
+      </c>
+      <c r="D115" t="s">
+        <v>31</v>
+      </c>
+      <c r="E115" t="s">
+        <v>41</v>
+      </c>
+      <c r="F115" t="s">
+        <v>33</v>
+      </c>
+      <c r="G115" t="s">
+        <v>45</v>
+      </c>
+      <c r="H115" t="s">
+        <v>35</v>
+      </c>
+      <c r="I115">
+        <v>17</v>
+      </c>
+      <c r="J115" t="s">
+        <v>36</v>
+      </c>
+      <c r="K115">
+        <v>604</v>
+      </c>
+      <c r="L115">
+        <v>1.438742</v>
+      </c>
+      <c r="M115">
+        <v>54.352941180000002</v>
+      </c>
+      <c r="N115" t="s">
+        <v>44</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>924</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>52</v>
+      </c>
+      <c r="R115">
+        <v>869</v>
+      </c>
+      <c r="S115">
+        <v>1063.2911389999999</v>
+      </c>
+      <c r="T115">
+        <v>17</v>
+      </c>
+      <c r="V115">
+        <v>54.352941000000001</v>
+      </c>
+      <c r="W115">
+        <v>1.956272</v>
+      </c>
+      <c r="X115">
+        <v>18</v>
+      </c>
+      <c r="Y115">
+        <v>2.0713460000000001</v>
+      </c>
+      <c r="Z115">
+        <v>51.333333000000003</v>
+      </c>
+    </row>
+    <row r="116" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>28</v>
+      </c>
+      <c r="B116" t="s">
+        <v>29</v>
+      </c>
+      <c r="C116" t="s">
+        <v>53</v>
+      </c>
+      <c r="D116" t="s">
+        <v>31</v>
+      </c>
+      <c r="E116" t="s">
+        <v>42</v>
+      </c>
+      <c r="F116" t="s">
+        <v>33</v>
+      </c>
+      <c r="G116" t="s">
+        <v>45</v>
+      </c>
+      <c r="H116" t="s">
+        <v>35</v>
+      </c>
+      <c r="I116">
+        <v>68</v>
+      </c>
+      <c r="J116" t="s">
+        <v>36</v>
+      </c>
+      <c r="K116">
+        <v>1090</v>
+      </c>
+      <c r="L116">
+        <v>1.2816510000000001</v>
+      </c>
+      <c r="M116">
+        <v>45.705882350000003</v>
+      </c>
+      <c r="N116" t="s">
+        <v>44</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>3108</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>52</v>
+      </c>
+      <c r="R116">
+        <v>1397</v>
+      </c>
+      <c r="S116">
+        <v>2224.7673589999999</v>
+      </c>
+      <c r="T116">
+        <v>68</v>
+      </c>
+      <c r="V116">
+        <v>45.705882000000003</v>
+      </c>
+      <c r="W116">
+        <v>4.8675730000000001</v>
+      </c>
+      <c r="X116">
+        <v>68</v>
+      </c>
+      <c r="Y116">
+        <v>4.8675730000000001</v>
+      </c>
+      <c r="Z116">
+        <v>45.705882000000003</v>
+      </c>
+    </row>
+    <row r="117" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>28</v>
+      </c>
+      <c r="B117" t="s">
+        <v>29</v>
+      </c>
+      <c r="C117" t="s">
+        <v>51</v>
+      </c>
+      <c r="D117" t="s">
+        <v>31</v>
+      </c>
+      <c r="E117" t="s">
+        <v>32</v>
+      </c>
+      <c r="F117" t="s">
+        <v>33</v>
+      </c>
+      <c r="G117" t="s">
+        <v>50</v>
+      </c>
+      <c r="H117" t="s">
+        <v>35</v>
+      </c>
+      <c r="I117">
+        <v>128</v>
+      </c>
+      <c r="J117" t="s">
+        <v>36</v>
+      </c>
+      <c r="K117">
+        <v>1541</v>
+      </c>
+      <c r="L117">
+        <v>1.341337</v>
+      </c>
+      <c r="M117">
+        <v>10.7109375</v>
+      </c>
+      <c r="N117" t="s">
+        <v>44</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>1371</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>49</v>
+      </c>
+      <c r="R117">
+        <v>2067</v>
+      </c>
+      <c r="S117">
+        <v>663.28011600000002</v>
+      </c>
+      <c r="T117">
+        <v>128</v>
+      </c>
+      <c r="V117">
+        <v>10.710938000000001</v>
+      </c>
+      <c r="W117">
+        <v>6.1925499999999998</v>
+      </c>
+      <c r="X117">
+        <v>150</v>
+      </c>
+      <c r="Y117">
+        <v>7.256894</v>
+      </c>
+      <c r="Z117">
+        <v>9.14</v>
+      </c>
+      <c r="AA117">
+        <v>112</v>
+      </c>
+      <c r="AB117">
+        <v>12.241071</v>
+      </c>
+    </row>
+    <row r="118" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>28</v>
+      </c>
+      <c r="B118" t="s">
+        <v>29</v>
+      </c>
+      <c r="C118" t="s">
+        <v>51</v>
+      </c>
+      <c r="D118" t="s">
+        <v>31</v>
+      </c>
+      <c r="E118" t="s">
+        <v>39</v>
+      </c>
+      <c r="F118" t="s">
+        <v>33</v>
+      </c>
+      <c r="G118" t="s">
+        <v>50</v>
+      </c>
+      <c r="H118" t="s">
+        <v>35</v>
+      </c>
+      <c r="I118">
+        <v>8</v>
+      </c>
+      <c r="J118" t="s">
+        <v>36</v>
+      </c>
+      <c r="K118">
+        <v>199</v>
+      </c>
+      <c r="L118">
+        <v>1.1859299999999999</v>
+      </c>
+      <c r="M118">
+        <v>12.625</v>
+      </c>
+      <c r="N118" t="s">
+        <v>44</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>101</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>49</v>
+      </c>
+      <c r="R118">
+        <v>236</v>
+      </c>
+      <c r="S118">
+        <v>427.96610199999998</v>
+      </c>
+      <c r="T118">
+        <v>8</v>
+      </c>
+      <c r="V118">
+        <v>12.625</v>
+      </c>
+      <c r="W118">
+        <v>3.389831</v>
+      </c>
+      <c r="X118">
+        <v>9</v>
+      </c>
+      <c r="Y118">
+        <v>3.8135590000000001</v>
+      </c>
+      <c r="Z118">
+        <v>11.222222</v>
+      </c>
+      <c r="AA118">
+        <v>5</v>
+      </c>
+      <c r="AB118">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>28</v>
+      </c>
+      <c r="B119" t="s">
+        <v>29</v>
+      </c>
+      <c r="C119" t="s">
+        <v>51</v>
+      </c>
+      <c r="D119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E119" t="s">
+        <v>40</v>
+      </c>
+      <c r="F119" t="s">
+        <v>33</v>
+      </c>
+      <c r="G119" t="s">
+        <v>50</v>
+      </c>
+      <c r="H119" t="s">
+        <v>35</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119" t="s">
+        <v>36</v>
+      </c>
+      <c r="K119">
+        <v>64</v>
+      </c>
+      <c r="L119">
+        <v>1.0625</v>
+      </c>
+      <c r="M119">
+        <v>7</v>
+      </c>
+      <c r="N119" t="s">
+        <v>44</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>7</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>49</v>
+      </c>
+      <c r="R119">
+        <v>68</v>
+      </c>
+      <c r="S119">
+        <v>102.941176</v>
+      </c>
+      <c r="T119">
+        <v>1</v>
+      </c>
+      <c r="V119">
+        <v>7</v>
+      </c>
+      <c r="W119">
+        <v>1.470588</v>
+      </c>
+      <c r="X119">
+        <v>1</v>
+      </c>
+      <c r="Y119">
+        <v>1.470588</v>
+      </c>
+      <c r="Z119">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>28</v>
+      </c>
+      <c r="B120" t="s">
+        <v>29</v>
+      </c>
+      <c r="C120" t="s">
+        <v>51</v>
+      </c>
+      <c r="D120" t="s">
+        <v>31</v>
+      </c>
+      <c r="E120" t="s">
+        <v>41</v>
+      </c>
+      <c r="F120" t="s">
+        <v>33</v>
+      </c>
+      <c r="G120" t="s">
+        <v>50</v>
+      </c>
+      <c r="H120" t="s">
+        <v>35</v>
+      </c>
+      <c r="I120">
+        <v>57</v>
+      </c>
+      <c r="J120" t="s">
+        <v>36</v>
+      </c>
+      <c r="K120">
+        <v>726</v>
+      </c>
+      <c r="L120">
+        <v>1.216253</v>
+      </c>
+      <c r="M120">
+        <v>8.8771929800000002</v>
+      </c>
+      <c r="N120" t="s">
+        <v>44</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>506</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>49</v>
+      </c>
+      <c r="R120">
+        <v>883</v>
+      </c>
+      <c r="S120">
+        <v>573.04643299999998</v>
+      </c>
+      <c r="T120">
+        <v>57</v>
+      </c>
+      <c r="V120">
+        <v>8.8771930000000001</v>
+      </c>
+      <c r="W120">
+        <v>6.4552659999999999</v>
+      </c>
+      <c r="X120">
+        <v>64</v>
+      </c>
+      <c r="Y120">
+        <v>7.2480180000000001</v>
+      </c>
+      <c r="Z120">
+        <v>7.90625</v>
+      </c>
+      <c r="AA120">
+        <v>48</v>
+      </c>
+      <c r="AB120">
+        <v>10.541667</v>
+      </c>
+    </row>
+    <row r="121" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>28</v>
+      </c>
+      <c r="B121" t="s">
+        <v>29</v>
+      </c>
+      <c r="C121" t="s">
+        <v>51</v>
+      </c>
+      <c r="D121" t="s">
+        <v>31</v>
+      </c>
+      <c r="E121" t="s">
+        <v>42</v>
+      </c>
+      <c r="F121" t="s">
+        <v>33</v>
+      </c>
+      <c r="G121" t="s">
+        <v>50</v>
+      </c>
+      <c r="H121" t="s">
+        <v>35</v>
+      </c>
+      <c r="I121">
+        <v>134</v>
+      </c>
+      <c r="J121" t="s">
+        <v>36</v>
+      </c>
+      <c r="K121">
+        <v>1326</v>
+      </c>
+      <c r="L121">
+        <v>1.320513</v>
+      </c>
+      <c r="M121">
+        <v>10.40298507</v>
+      </c>
+      <c r="N121" t="s">
+        <v>44</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>1394</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>49</v>
+      </c>
+      <c r="R121">
+        <v>1751</v>
+      </c>
+      <c r="S121">
+        <v>796.11650499999996</v>
+      </c>
+      <c r="T121">
+        <v>134</v>
+      </c>
+      <c r="V121">
+        <v>10.402984999999999</v>
+      </c>
+      <c r="W121">
+        <v>7.6527700000000003</v>
+      </c>
+      <c r="X121">
+        <v>152</v>
+      </c>
+      <c r="Y121">
+        <v>8.6807540000000003</v>
+      </c>
+      <c r="Z121">
+        <v>9.1710530000000006</v>
+      </c>
+      <c r="AA121">
+        <v>118</v>
+      </c>
+      <c r="AB121">
+        <v>11.813559</v>
+      </c>
+    </row>
+    <row r="122" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>28</v>
+      </c>
+      <c r="B122" t="s">
+        <v>29</v>
+      </c>
+      <c r="C122" t="s">
+        <v>48</v>
+      </c>
+      <c r="D122" t="s">
+        <v>31</v>
+      </c>
+      <c r="E122" t="s">
+        <v>32</v>
+      </c>
+      <c r="F122" t="s">
+        <v>33</v>
+      </c>
+      <c r="G122" t="s">
+        <v>45</v>
+      </c>
+      <c r="H122" t="s">
+        <v>35</v>
+      </c>
+      <c r="I122">
+        <v>3</v>
+      </c>
+      <c r="J122" t="s">
+        <v>36</v>
+      </c>
+      <c r="K122">
+        <v>88</v>
+      </c>
+      <c r="L122">
+        <v>1.1136360000000001</v>
+      </c>
+      <c r="M122">
+        <v>33</v>
+      </c>
+      <c r="N122" t="s">
+        <v>44</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>99</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>47</v>
+      </c>
+      <c r="R122">
+        <v>98</v>
+      </c>
+      <c r="S122">
+        <v>1010.204082</v>
+      </c>
+      <c r="T122">
+        <v>3</v>
+      </c>
+      <c r="V122">
+        <v>33</v>
+      </c>
+      <c r="W122">
+        <v>3.0612240000000002</v>
+      </c>
+      <c r="X122">
+        <v>3</v>
+      </c>
+      <c r="Y122">
+        <v>3.0612240000000002</v>
+      </c>
+      <c r="Z122">
+        <v>33</v>
+      </c>
+      <c r="AA122">
+        <v>3</v>
+      </c>
+      <c r="AB122">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="123" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>28</v>
+      </c>
+      <c r="B123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C123" t="s">
+        <v>48</v>
+      </c>
+      <c r="D123" t="s">
+        <v>31</v>
+      </c>
+      <c r="E123" t="s">
+        <v>39</v>
+      </c>
+      <c r="F123" t="s">
+        <v>33</v>
+      </c>
+      <c r="G123" t="s">
+        <v>45</v>
+      </c>
+      <c r="H123" t="s">
+        <v>35</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123" t="s">
+        <v>36</v>
+      </c>
+      <c r="K123">
+        <v>9</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="M123">
+        <v>9</v>
+      </c>
+      <c r="N123" t="s">
+        <v>44</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>9</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>47</v>
+      </c>
+      <c r="R123">
+        <v>9</v>
+      </c>
+      <c r="S123">
+        <v>1000</v>
+      </c>
+      <c r="T123">
+        <v>1</v>
+      </c>
+      <c r="V123">
+        <v>9</v>
+      </c>
+      <c r="W123">
+        <v>11.111110999999999</v>
+      </c>
+      <c r="X123">
+        <v>1</v>
+      </c>
+      <c r="Y123">
+        <v>11.111110999999999</v>
+      </c>
+      <c r="Z123">
+        <v>9</v>
+      </c>
+      <c r="AA123">
+        <v>1</v>
+      </c>
+      <c r="AB123">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>28</v>
+      </c>
+      <c r="B124" t="s">
+        <v>29</v>
+      </c>
+      <c r="C124" t="s">
+        <v>48</v>
+      </c>
+      <c r="D124" t="s">
+        <v>31</v>
+      </c>
+      <c r="E124" t="s">
+        <v>40</v>
+      </c>
+      <c r="F124" t="s">
+        <v>33</v>
+      </c>
+      <c r="G124" t="s">
+        <v>45</v>
+      </c>
+      <c r="H124" t="s">
+        <v>35</v>
+      </c>
+      <c r="K124">
+        <v>1</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="N124" t="s">
+        <v>44</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>47</v>
+      </c>
+      <c r="R124">
+        <v>1</v>
+      </c>
+      <c r="S124">
+        <v>0</v>
+      </c>
+      <c r="X124">
+        <v>0</v>
+      </c>
+      <c r="Y124">
+        <v>0</v>
+      </c>
+      <c r="Z124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>28</v>
+      </c>
+      <c r="B125" t="s">
+        <v>29</v>
+      </c>
+      <c r="C125" t="s">
+        <v>48</v>
+      </c>
+      <c r="D125" t="s">
+        <v>31</v>
+      </c>
+      <c r="E125" t="s">
+        <v>41</v>
+      </c>
+      <c r="F125" t="s">
+        <v>33</v>
+      </c>
+      <c r="G125" t="s">
+        <v>45</v>
+      </c>
+      <c r="H125" t="s">
+        <v>35</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="J125" t="s">
+        <v>36</v>
+      </c>
+      <c r="K125">
+        <v>29</v>
+      </c>
+      <c r="L125">
+        <v>1.1724140000000001</v>
+      </c>
+      <c r="M125">
+        <v>24</v>
+      </c>
+      <c r="N125" t="s">
+        <v>44</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>24</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>47</v>
+      </c>
+      <c r="R125">
+        <v>34</v>
+      </c>
+      <c r="S125">
+        <v>705.88235299999997</v>
+      </c>
+      <c r="T125">
+        <v>1</v>
+      </c>
+      <c r="V125">
+        <v>24</v>
+      </c>
+      <c r="W125">
+        <v>2.941176</v>
+      </c>
+      <c r="X125">
+        <v>1</v>
+      </c>
+      <c r="Y125">
+        <v>2.941176</v>
+      </c>
+      <c r="Z125">
+        <v>24</v>
+      </c>
+      <c r="AA125">
+        <v>1</v>
+      </c>
+      <c r="AB125">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>28</v>
+      </c>
+      <c r="B126" t="s">
+        <v>29</v>
+      </c>
+      <c r="C126" t="s">
+        <v>48</v>
+      </c>
+      <c r="D126" t="s">
+        <v>31</v>
+      </c>
+      <c r="E126" t="s">
+        <v>42</v>
+      </c>
+      <c r="F126" t="s">
+        <v>33</v>
+      </c>
+      <c r="G126" t="s">
+        <v>45</v>
+      </c>
+      <c r="H126" t="s">
+        <v>35</v>
+      </c>
+      <c r="I126">
+        <v>10</v>
+      </c>
+      <c r="J126" t="s">
+        <v>36</v>
+      </c>
+      <c r="K126">
+        <v>753</v>
+      </c>
+      <c r="L126">
+        <v>1.098274</v>
+      </c>
+      <c r="M126">
+        <v>55.6</v>
+      </c>
+      <c r="N126" t="s">
+        <v>44</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>556</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>47</v>
+      </c>
+      <c r="R126">
+        <v>827</v>
+      </c>
+      <c r="S126">
+        <v>672.30955300000005</v>
+      </c>
+      <c r="T126">
+        <v>10</v>
+      </c>
+      <c r="V126">
+        <v>55.6</v>
+      </c>
+      <c r="W126">
+        <v>1.20919</v>
+      </c>
+      <c r="X126">
+        <v>10</v>
+      </c>
+      <c r="Y126">
+        <v>1.20919</v>
+      </c>
+      <c r="Z126">
+        <v>55.6</v>
+      </c>
+      <c r="AA126">
+        <v>3</v>
+      </c>
+      <c r="AB126">
+        <v>185.33333300000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>28</v>
+      </c>
+      <c r="B127" t="s">
+        <v>29</v>
+      </c>
+      <c r="C127" t="s">
+        <v>46</v>
+      </c>
+      <c r="D127" t="s">
+        <v>31</v>
+      </c>
+      <c r="E127" t="s">
+        <v>32</v>
+      </c>
+      <c r="F127" t="s">
+        <v>33</v>
+      </c>
+      <c r="G127" t="s">
+        <v>45</v>
+      </c>
+      <c r="H127" t="s">
+        <v>35</v>
+      </c>
+      <c r="I127">
+        <v>5</v>
+      </c>
+      <c r="J127" t="s">
+        <v>36</v>
+      </c>
+      <c r="K127">
+        <v>176</v>
+      </c>
+      <c r="L127">
+        <v>1.0511360000000001</v>
+      </c>
+      <c r="M127">
+        <v>32.6</v>
+      </c>
+      <c r="N127" t="s">
+        <v>44</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>163</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>43</v>
+      </c>
+      <c r="R127">
+        <v>185</v>
+      </c>
+      <c r="S127">
+        <v>881.08108100000004</v>
+      </c>
+      <c r="T127">
+        <v>5</v>
+      </c>
+      <c r="V127">
+        <v>32.6</v>
+      </c>
+      <c r="W127">
+        <v>2.7027030000000001</v>
+      </c>
+      <c r="X127">
+        <v>5</v>
+      </c>
+      <c r="Y127">
+        <v>2.7027030000000001</v>
+      </c>
+      <c r="Z127">
+        <v>32.6</v>
+      </c>
+      <c r="AA127">
+        <v>4</v>
+      </c>
+      <c r="AB127">
+        <v>40.75</v>
+      </c>
+    </row>
+    <row r="128" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>28</v>
+      </c>
+      <c r="B128" t="s">
+        <v>29</v>
+      </c>
+      <c r="C128" t="s">
+        <v>46</v>
+      </c>
+      <c r="D128" t="s">
+        <v>31</v>
+      </c>
+      <c r="E128" t="s">
+        <v>39</v>
+      </c>
+      <c r="F128" t="s">
+        <v>33</v>
+      </c>
+      <c r="G128" t="s">
+        <v>45</v>
+      </c>
+      <c r="H128" t="s">
+        <v>35</v>
+      </c>
+      <c r="K128">
+        <v>5</v>
+      </c>
+      <c r="L128">
+        <v>1.2</v>
+      </c>
+      <c r="N128" t="s">
+        <v>44</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>6</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>43</v>
+      </c>
+      <c r="R128">
+        <v>6</v>
+      </c>
+      <c r="S128">
+        <v>1000</v>
+      </c>
+      <c r="X128">
+        <v>0</v>
+      </c>
+      <c r="Y128">
+        <v>0</v>
+      </c>
+      <c r="Z128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>28</v>
+      </c>
+      <c r="B129" t="s">
+        <v>29</v>
+      </c>
+      <c r="C129" t="s">
+        <v>46</v>
+      </c>
+      <c r="D129" t="s">
+        <v>31</v>
+      </c>
+      <c r="E129" t="s">
+        <v>41</v>
+      </c>
+      <c r="F129" t="s">
+        <v>33</v>
+      </c>
+      <c r="G129" t="s">
+        <v>45</v>
+      </c>
+      <c r="H129" t="s">
+        <v>35</v>
+      </c>
+      <c r="I129">
+        <v>2</v>
+      </c>
+      <c r="J129" t="s">
+        <v>36</v>
+      </c>
+      <c r="K129">
+        <v>88</v>
+      </c>
+      <c r="L129">
+        <v>1.0113639999999999</v>
+      </c>
+      <c r="M129">
+        <v>33.5</v>
+      </c>
+      <c r="N129" t="s">
+        <v>44</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>67</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>43</v>
+      </c>
+      <c r="R129">
+        <v>89</v>
+      </c>
+      <c r="S129">
+        <v>752.808989</v>
+      </c>
+      <c r="T129">
+        <v>2</v>
+      </c>
+      <c r="V129">
+        <v>33.5</v>
+      </c>
+      <c r="W129">
+        <v>2.2471909999999999</v>
+      </c>
+      <c r="X129">
+        <v>2</v>
+      </c>
+      <c r="Y129">
+        <v>2.2471909999999999</v>
+      </c>
+      <c r="Z129">
+        <v>33.5</v>
+      </c>
+      <c r="AA129">
+        <v>2</v>
+      </c>
+      <c r="AB129">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>28</v>
+      </c>
+      <c r="B130" t="s">
+        <v>29</v>
+      </c>
+      <c r="C130" t="s">
+        <v>46</v>
+      </c>
+      <c r="D130" t="s">
+        <v>31</v>
+      </c>
+      <c r="E130" t="s">
+        <v>42</v>
+      </c>
+      <c r="F130" t="s">
+        <v>33</v>
+      </c>
+      <c r="G130" t="s">
+        <v>45</v>
+      </c>
+      <c r="H130" t="s">
+        <v>35</v>
+      </c>
+      <c r="I130">
+        <v>3</v>
+      </c>
+      <c r="J130" t="s">
+        <v>36</v>
+      </c>
+      <c r="K130">
+        <v>60</v>
+      </c>
+      <c r="L130">
+        <v>1.016667</v>
+      </c>
+      <c r="M130">
+        <v>26.333333329999999</v>
+      </c>
+      <c r="N130" t="s">
+        <v>44</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>79</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>43</v>
+      </c>
+      <c r="R130">
+        <v>61</v>
+      </c>
+      <c r="S130">
+        <v>1295.0819670000001</v>
+      </c>
+      <c r="T130">
+        <v>3</v>
+      </c>
+      <c r="V130">
+        <v>26.333333</v>
+      </c>
+      <c r="W130">
+        <v>4.9180330000000003</v>
+      </c>
+      <c r="X130">
+        <v>3</v>
+      </c>
+      <c r="Y130">
+        <v>4.9180330000000003</v>
+      </c>
+      <c r="Z130">
+        <v>26.333333</v>
+      </c>
+      <c r="AA130">
+        <v>3</v>
+      </c>
+      <c r="AB130">
+        <v>26.333333</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>